--- a/compare/output/dscale_GreenElec_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_GreenElec_downscaled_SSP460.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1473.464389</v>
+        <v>1473.465171</v>
       </c>
       <c r="F2" t="n">
-        <v>3911.163633</v>
+        <v>3911.16905</v>
       </c>
       <c r="G2" t="n">
-        <v>7519.208166</v>
+        <v>7519.230474</v>
       </c>
       <c r="H2" t="n">
-        <v>11818.272858</v>
+        <v>11818.352393</v>
       </c>
       <c r="I2" t="n">
-        <v>16110.323108</v>
+        <v>16110.652817</v>
       </c>
       <c r="J2" t="n">
         <v>3200.22298</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>126.44408</v>
+        <v>126.444102</v>
       </c>
       <c r="F3" t="n">
-        <v>291.425821</v>
+        <v>291.425967</v>
       </c>
       <c r="G3" t="n">
-        <v>503.298916</v>
+        <v>503.299495</v>
       </c>
       <c r="H3" t="n">
-        <v>738.453981</v>
+        <v>738.456114</v>
       </c>
       <c r="I3" t="n">
-        <v>975.048947</v>
+        <v>975.058231</v>
       </c>
       <c r="J3" t="n">
         <v>775.288616</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>147.048801</v>
+        <v>147.048495</v>
       </c>
       <c r="F4" t="n">
-        <v>315.065122</v>
+        <v>315.063557</v>
       </c>
       <c r="G4" t="n">
-        <v>491.033912</v>
+        <v>491.029328</v>
       </c>
       <c r="H4" t="n">
-        <v>668.305263</v>
+        <v>668.292745</v>
       </c>
       <c r="I4" t="n">
-        <v>840.34962</v>
+        <v>840.305575</v>
       </c>
       <c r="J4" t="n">
         <v>3361.172544</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>78.152433</v>
+        <v>78.152288</v>
       </c>
       <c r="F5" t="n">
-        <v>244.491494</v>
+        <v>244.489683</v>
       </c>
       <c r="G5" t="n">
-        <v>590.145134</v>
+        <v>590.130449</v>
       </c>
       <c r="H5" t="n">
-        <v>1107.994805</v>
+        <v>1107.912001</v>
       </c>
       <c r="I5" t="n">
-        <v>1715.633972</v>
+        <v>1715.179509</v>
       </c>
       <c r="J5" t="n">
         <v>32562.973694</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37125.772844</v>
+        <v>37125.789107</v>
       </c>
       <c r="F6" t="n">
-        <v>98137.50664399999</v>
+        <v>98137.615024</v>
       </c>
       <c r="G6" t="n">
-        <v>172875.287703</v>
+        <v>172875.704854</v>
       </c>
       <c r="H6" t="n">
-        <v>254166.01542</v>
+        <v>254167.447725</v>
       </c>
       <c r="I6" t="n">
-        <v>337721.210002</v>
+        <v>337727.096061</v>
       </c>
       <c r="J6" t="n">
         <v>122274.165939</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29573.44962</v>
+        <v>29573.459791</v>
       </c>
       <c r="F7" t="n">
-        <v>80682.22475199999</v>
+        <v>80682.28892399999</v>
       </c>
       <c r="G7" t="n">
-        <v>164337.912813</v>
+        <v>164338.145285</v>
       </c>
       <c r="H7" t="n">
-        <v>276964.699711</v>
+        <v>276965.4363</v>
       </c>
       <c r="I7" t="n">
-        <v>409089.320112</v>
+        <v>409092.04187</v>
       </c>
       <c r="J7" t="n">
         <v>463958.683551</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3381.853511</v>
+        <v>3381.854317</v>
       </c>
       <c r="F8" t="n">
-        <v>9125.596401999999</v>
+        <v>9125.601015</v>
       </c>
       <c r="G8" t="n">
-        <v>18157.672793</v>
+        <v>18157.687615</v>
       </c>
       <c r="H8" t="n">
-        <v>29871.104752</v>
+        <v>29871.148529</v>
       </c>
       <c r="I8" t="n">
-        <v>43038.577057</v>
+        <v>43038.73632</v>
       </c>
       <c r="J8" t="n">
         <v>53286.666217</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2419.199359</v>
+        <v>2419.182708</v>
       </c>
       <c r="F9" t="n">
-        <v>5004.369084</v>
+        <v>5004.282738</v>
       </c>
       <c r="G9" t="n">
-        <v>7362.98395</v>
+        <v>7362.73841</v>
       </c>
       <c r="H9" t="n">
-        <v>9316.645317</v>
+        <v>9316.018993</v>
       </c>
       <c r="I9" t="n">
-        <v>10871.100011</v>
+        <v>10869.080905</v>
       </c>
       <c r="J9" t="n">
         <v>110032.812943</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1072.817032</v>
+        <v>1072.816292</v>
       </c>
       <c r="F10" t="n">
-        <v>2548.529605</v>
+        <v>2548.525138</v>
       </c>
       <c r="G10" t="n">
-        <v>4254.459793</v>
+        <v>4254.446023</v>
       </c>
       <c r="H10" t="n">
-        <v>6156.04532</v>
+        <v>6156.006835</v>
       </c>
       <c r="I10" t="n">
-        <v>8102.333526</v>
+        <v>8102.200851</v>
       </c>
       <c r="J10" t="n">
         <v>17634.211396</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29960.707004</v>
+        <v>29960.694492</v>
       </c>
       <c r="F11" t="n">
-        <v>76382.337967</v>
+        <v>76382.234914</v>
       </c>
       <c r="G11" t="n">
-        <v>141656.457679</v>
+        <v>141655.987205</v>
       </c>
       <c r="H11" t="n">
-        <v>221073.222985</v>
+        <v>221071.445544</v>
       </c>
       <c r="I11" t="n">
-        <v>304135.913117</v>
+        <v>304128.34552</v>
       </c>
       <c r="J11" t="n">
         <v>832515.625242</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1585.369893</v>
+        <v>1585.370663</v>
       </c>
       <c r="F12" t="n">
-        <v>4258.202395</v>
+        <v>4258.207664</v>
       </c>
       <c r="G12" t="n">
-        <v>8462.479648</v>
+        <v>8462.501458000001</v>
       </c>
       <c r="H12" t="n">
-        <v>14022.912793</v>
+        <v>14022.992708</v>
       </c>
       <c r="I12" t="n">
-        <v>20192.270156</v>
+        <v>20192.613176</v>
       </c>
       <c r="J12" t="n">
         <v>8859.70694</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12298.298034</v>
+        <v>12298.299574</v>
       </c>
       <c r="F13" t="n">
-        <v>31636.398781</v>
+        <v>31636.408024</v>
       </c>
       <c r="G13" t="n">
-        <v>58150.400795</v>
+        <v>58150.440703</v>
       </c>
       <c r="H13" t="n">
-        <v>91228.983097</v>
+        <v>91229.14641099999</v>
       </c>
       <c r="I13" t="n">
-        <v>129367.717671</v>
+        <v>129368.486466</v>
       </c>
       <c r="J13" t="n">
         <v>138411.412238</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>800.558316</v>
+        <v>800.203942</v>
       </c>
       <c r="F14" t="n">
-        <v>2111.249696</v>
+        <v>2108.881087</v>
       </c>
       <c r="G14" t="n">
-        <v>4748.856852</v>
+        <v>4737.947222</v>
       </c>
       <c r="H14" t="n">
-        <v>7561.016887</v>
+        <v>7525.010784</v>
       </c>
       <c r="I14" t="n">
-        <v>10937.446367</v>
+        <v>10802.125499</v>
       </c>
       <c r="J14" t="n">
         <v>319945.692523</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>56957.377621</v>
+        <v>56957.96743</v>
       </c>
       <c r="F15" t="n">
-        <v>165724.151193</v>
+        <v>165727.827121</v>
       </c>
       <c r="G15" t="n">
-        <v>390358.292557</v>
+        <v>390373.674978</v>
       </c>
       <c r="H15" t="n">
-        <v>631404.156583</v>
+        <v>631451.727272</v>
       </c>
       <c r="I15" t="n">
-        <v>905121.749088</v>
+        <v>905294.7271359999</v>
       </c>
       <c r="J15" t="n">
         <v>804198.67333</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29.438707</v>
+        <v>29.053908</v>
       </c>
       <c r="F16" t="n">
-        <v>70.196876</v>
+        <v>68.11886800000001</v>
       </c>
       <c r="G16" t="n">
-        <v>139.791153</v>
+        <v>132.43703</v>
       </c>
       <c r="H16" t="n">
-        <v>210.735197</v>
+        <v>191.004776</v>
       </c>
       <c r="I16" t="n">
-        <v>336.800316</v>
+        <v>272.772373</v>
       </c>
       <c r="J16" t="n">
         <v>131559.45515</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15887.840641</v>
+        <v>15888.079747</v>
       </c>
       <c r="F17" t="n">
-        <v>41620.784564</v>
+        <v>41622.273813</v>
       </c>
       <c r="G17" t="n">
-        <v>89827.46251300001</v>
+        <v>89833.711497</v>
       </c>
       <c r="H17" t="n">
-        <v>135220.010914</v>
+        <v>135239.055651</v>
       </c>
       <c r="I17" t="n">
-        <v>182022.351601</v>
+        <v>182089.210695</v>
       </c>
       <c r="J17" t="n">
         <v>82941.017052</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1992.72465</v>
+        <v>1992.634908</v>
       </c>
       <c r="F18" t="n">
-        <v>5661.08293</v>
+        <v>5660.364371</v>
       </c>
       <c r="G18" t="n">
-        <v>12626.636026</v>
+        <v>12623.268373</v>
       </c>
       <c r="H18" t="n">
-        <v>19565.471218</v>
+        <v>19554.592317</v>
       </c>
       <c r="I18" t="n">
-        <v>27565.393428</v>
+        <v>27524.905097</v>
       </c>
       <c r="J18" t="n">
         <v>131017.007745</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18777.665287</v>
+        <v>18777.59011</v>
       </c>
       <c r="F19" t="n">
-        <v>27195.211153</v>
+        <v>27194.923726</v>
       </c>
       <c r="G19" t="n">
-        <v>37354.608468</v>
+        <v>37353.795151</v>
       </c>
       <c r="H19" t="n">
-        <v>53194.976746</v>
+        <v>53192.589324</v>
       </c>
       <c r="I19" t="n">
-        <v>69511.746375</v>
+        <v>69503.64767400001</v>
       </c>
       <c r="J19" t="n">
         <v>349005.525538</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.961544</v>
+        <v>10.930034</v>
       </c>
       <c r="F20" t="n">
-        <v>16.049853</v>
+        <v>15.927637</v>
       </c>
       <c r="G20" t="n">
-        <v>24.073213</v>
+        <v>23.696754</v>
       </c>
       <c r="H20" t="n">
-        <v>39.302691</v>
+        <v>38.155078</v>
       </c>
       <c r="I20" t="n">
-        <v>71.383984</v>
+        <v>67.532309</v>
       </c>
       <c r="J20" t="n">
         <v>119751.260642</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>345.814702</v>
+        <v>345.813935</v>
       </c>
       <c r="F21" t="n">
-        <v>398.878059</v>
+        <v>398.875995</v>
       </c>
       <c r="G21" t="n">
-        <v>457.658022</v>
+        <v>457.653515</v>
       </c>
       <c r="H21" t="n">
-        <v>576.579963</v>
+        <v>576.568551</v>
       </c>
       <c r="I21" t="n">
-        <v>694.3622800000001</v>
+        <v>694.326099</v>
       </c>
       <c r="J21" t="n">
         <v>1950.793012</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61270.809466</v>
+        <v>61270.881478</v>
       </c>
       <c r="F22" t="n">
-        <v>89796.99135700001</v>
+        <v>89797.270284</v>
       </c>
       <c r="G22" t="n">
-        <v>123557.495928</v>
+        <v>123558.292594</v>
       </c>
       <c r="H22" t="n">
-        <v>174777.472424</v>
+        <v>174779.787529</v>
       </c>
       <c r="I22" t="n">
-        <v>225590.277307</v>
+        <v>225597.901297</v>
       </c>
       <c r="J22" t="n">
         <v>33033.717996</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2648.604823</v>
+        <v>2648.604464</v>
       </c>
       <c r="F23" t="n">
-        <v>4140.128093</v>
+        <v>4140.125973</v>
       </c>
       <c r="G23" t="n">
-        <v>6217.953159</v>
+        <v>6217.944369</v>
       </c>
       <c r="H23" t="n">
-        <v>9770.917335</v>
+        <v>9770.880224</v>
       </c>
       <c r="I23" t="n">
-        <v>14102.53371</v>
+        <v>14102.358968</v>
       </c>
       <c r="J23" t="n">
         <v>26462.913697</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5392.340616</v>
+        <v>5392.334924</v>
       </c>
       <c r="F24" t="n">
-        <v>7355.295094</v>
+        <v>7355.274213</v>
       </c>
       <c r="G24" t="n">
-        <v>9837.831655</v>
+        <v>9837.770511999999</v>
       </c>
       <c r="H24" t="n">
-        <v>13633.531933</v>
+        <v>13633.346953</v>
       </c>
       <c r="I24" t="n">
-        <v>17313.088942</v>
+        <v>17312.444918</v>
       </c>
       <c r="J24" t="n">
         <v>41767.807558</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291.177974</v>
+        <v>1291.17617</v>
       </c>
       <c r="F25" t="n">
-        <v>1578.78064</v>
+        <v>1578.775328</v>
       </c>
       <c r="G25" t="n">
-        <v>1919.058633</v>
+        <v>1919.045734</v>
       </c>
       <c r="H25" t="n">
-        <v>2515.59286</v>
+        <v>2515.557404</v>
       </c>
       <c r="I25" t="n">
-        <v>3098.580196</v>
+        <v>3098.461951</v>
       </c>
       <c r="J25" t="n">
         <v>7390.110549</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7807.628591</v>
+        <v>7807.607677</v>
       </c>
       <c r="F26" t="n">
-        <v>10885.38765</v>
+        <v>10885.313044</v>
       </c>
       <c r="G26" t="n">
-        <v>14151.11865</v>
+        <v>14150.927986</v>
       </c>
       <c r="H26" t="n">
-        <v>19382.507659</v>
+        <v>19381.988517</v>
       </c>
       <c r="I26" t="n">
-        <v>24680.204251</v>
+        <v>24678.532573</v>
       </c>
       <c r="J26" t="n">
         <v>82555.72385900001</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>46598.813178</v>
+        <v>46598.853597</v>
       </c>
       <c r="F27" t="n">
-        <v>66673.900051</v>
+        <v>66674.05471900001</v>
       </c>
       <c r="G27" t="n">
-        <v>88190.00357</v>
+        <v>88190.436002</v>
       </c>
       <c r="H27" t="n">
-        <v>122591.544524</v>
+        <v>122592.793333</v>
       </c>
       <c r="I27" t="n">
-        <v>159407.621023</v>
+        <v>159411.777656</v>
       </c>
       <c r="J27" t="n">
         <v>63563.857582</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18204.08812</v>
+        <v>18204.111911</v>
       </c>
       <c r="F28" t="n">
-        <v>23371.396845</v>
+        <v>23371.477876</v>
       </c>
       <c r="G28" t="n">
-        <v>33099.336112</v>
+        <v>33099.574794</v>
       </c>
       <c r="H28" t="n">
-        <v>51175.884565</v>
+        <v>51176.643785</v>
       </c>
       <c r="I28" t="n">
-        <v>74223.597931</v>
+        <v>74226.412555</v>
       </c>
       <c r="J28" t="n">
         <v>1155.027267</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.252013</v>
+        <v>22.251959</v>
       </c>
       <c r="F29" t="n">
-        <v>35.16521</v>
+        <v>35.164979</v>
       </c>
       <c r="G29" t="n">
-        <v>49.954706</v>
+        <v>49.953959</v>
       </c>
       <c r="H29" t="n">
-        <v>66.848039</v>
+        <v>66.84571099999999</v>
       </c>
       <c r="I29" t="n">
-        <v>87.05142600000001</v>
+        <v>87.042078</v>
       </c>
       <c r="J29" t="n">
         <v>4397.568194</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>411.658199</v>
+        <v>411.658194</v>
       </c>
       <c r="F30" t="n">
-        <v>526.541453</v>
+        <v>526.541468</v>
       </c>
       <c r="G30" t="n">
-        <v>606.343975</v>
+        <v>606.344035</v>
       </c>
       <c r="H30" t="n">
-        <v>721.109317</v>
+        <v>721.109464</v>
       </c>
       <c r="I30" t="n">
-        <v>899.147423</v>
+        <v>899.147905</v>
       </c>
       <c r="J30" t="n">
         <v>971.809584</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>768.595547</v>
+        <v>768.595624</v>
       </c>
       <c r="F31" t="n">
-        <v>1169.89676</v>
+        <v>1169.897056</v>
       </c>
       <c r="G31" t="n">
-        <v>1533.820884</v>
+        <v>1533.821602</v>
       </c>
       <c r="H31" t="n">
-        <v>1934.850803</v>
+        <v>1934.852556</v>
       </c>
       <c r="I31" t="n">
-        <v>2406.050182</v>
+        <v>2406.056189</v>
       </c>
       <c r="J31" t="n">
         <v>465.868149</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5403.475372</v>
+        <v>5403.475813</v>
       </c>
       <c r="F32" t="n">
-        <v>7552.576477</v>
+        <v>7552.578081</v>
       </c>
       <c r="G32" t="n">
-        <v>9465.252038000001</v>
+        <v>9465.255725999999</v>
       </c>
       <c r="H32" t="n">
-        <v>11646.502058</v>
+        <v>11646.510694</v>
       </c>
       <c r="I32" t="n">
-        <v>14446.842367</v>
+        <v>14446.871386</v>
       </c>
       <c r="J32" t="n">
         <v>5997.730394</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16295.724179</v>
+        <v>16295.72562</v>
       </c>
       <c r="F33" t="n">
-        <v>24811.571297</v>
+        <v>24811.576836</v>
       </c>
       <c r="G33" t="n">
-        <v>33736.444021</v>
+        <v>33736.457479</v>
       </c>
       <c r="H33" t="n">
-        <v>43602.575025</v>
+        <v>43602.60745</v>
       </c>
       <c r="I33" t="n">
-        <v>55142.904721</v>
+        <v>55143.014608</v>
       </c>
       <c r="J33" t="n">
         <v>23060.892135</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33151.448779</v>
+        <v>33151.452413</v>
       </c>
       <c r="F34" t="n">
-        <v>89028.79726399999</v>
+        <v>89028.82189599999</v>
       </c>
       <c r="G34" t="n">
-        <v>205190.544402</v>
+        <v>205190.648037</v>
       </c>
       <c r="H34" t="n">
-        <v>382361.188287</v>
+        <v>382361.553806</v>
       </c>
       <c r="I34" t="n">
-        <v>611729.045624</v>
+        <v>611730.611534</v>
       </c>
       <c r="J34" t="n">
         <v>136861.518543</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4072.07702</v>
+        <v>4072.077308</v>
       </c>
       <c r="F35" t="n">
-        <v>7727.138531</v>
+        <v>7727.139659</v>
       </c>
       <c r="G35" t="n">
-        <v>12828.794423</v>
+        <v>12828.796365</v>
       </c>
       <c r="H35" t="n">
-        <v>18679.208095</v>
+        <v>18679.209166</v>
       </c>
       <c r="I35" t="n">
-        <v>24893.352714</v>
+        <v>24893.34643</v>
       </c>
       <c r="J35" t="n">
         <v>35340.681869</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>81.478013</v>
+        <v>81.477952</v>
       </c>
       <c r="F36" t="n">
-        <v>125.952664</v>
+        <v>125.952373</v>
       </c>
       <c r="G36" t="n">
-        <v>153.62582</v>
+        <v>153.625051</v>
       </c>
       <c r="H36" t="n">
-        <v>171.180954</v>
+        <v>171.179131</v>
       </c>
       <c r="I36" t="n">
-        <v>186.891633</v>
+        <v>186.886042</v>
       </c>
       <c r="J36" t="n">
         <v>2252.829064</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4535.659647</v>
+        <v>4535.659048</v>
       </c>
       <c r="F37" t="n">
-        <v>6110.453284</v>
+        <v>6110.451508</v>
       </c>
       <c r="G37" t="n">
-        <v>7326.680491</v>
+        <v>7326.6762</v>
       </c>
       <c r="H37" t="n">
-        <v>8544.790053999999</v>
+        <v>8544.779168999999</v>
       </c>
       <c r="I37" t="n">
-        <v>9980.254247999999</v>
+        <v>9980.217328000001</v>
       </c>
       <c r="J37" t="n">
         <v>26069.731084</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21688.072541</v>
+        <v>21688.074698</v>
       </c>
       <c r="F38" t="n">
-        <v>34539.011236</v>
+        <v>34539.019921</v>
       </c>
       <c r="G38" t="n">
-        <v>46880.627907</v>
+        <v>46880.649624</v>
       </c>
       <c r="H38" t="n">
-        <v>60631.808443</v>
+        <v>60631.862734</v>
       </c>
       <c r="I38" t="n">
-        <v>77865.906238</v>
+        <v>77866.097951</v>
       </c>
       <c r="J38" t="n">
         <v>17213.93211</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1746.003785</v>
+        <v>1746.00395</v>
       </c>
       <c r="F39" t="n">
-        <v>2448.475763</v>
+        <v>2448.476359</v>
       </c>
       <c r="G39" t="n">
-        <v>3128.843981</v>
+        <v>3128.845386</v>
       </c>
       <c r="H39" t="n">
-        <v>3904.101194</v>
+        <v>3904.104573</v>
       </c>
       <c r="I39" t="n">
-        <v>4857.680002</v>
+        <v>4857.691525</v>
       </c>
       <c r="J39" t="n">
         <v>1221.232783</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>266.118291</v>
+        <v>266.118313</v>
       </c>
       <c r="F40" t="n">
-        <v>409.019146</v>
+        <v>409.019233</v>
       </c>
       <c r="G40" t="n">
-        <v>550.982995</v>
+        <v>550.983199</v>
       </c>
       <c r="H40" t="n">
-        <v>693.579765</v>
+        <v>693.580242</v>
       </c>
       <c r="I40" t="n">
-        <v>859.303121</v>
+        <v>859.304703</v>
       </c>
       <c r="J40" t="n">
         <v>401.725291</v>
@@ -3493,16 +3493,16 @@
         <v>313.295926</v>
       </c>
       <c r="F41" t="n">
-        <v>538.438522</v>
+        <v>538.438492</v>
       </c>
       <c r="G41" t="n">
-        <v>756.025568</v>
+        <v>756.025393</v>
       </c>
       <c r="H41" t="n">
-        <v>978.4711589999999</v>
+        <v>978.470497</v>
       </c>
       <c r="I41" t="n">
-        <v>1226.638048</v>
+        <v>1226.635326</v>
       </c>
       <c r="J41" t="n">
         <v>2700.493037</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1731.945382</v>
+        <v>1731.941896</v>
       </c>
       <c r="F42" t="n">
-        <v>2578.966851</v>
+        <v>2578.95377</v>
       </c>
       <c r="G42" t="n">
-        <v>3399.620897</v>
+        <v>3399.584961</v>
       </c>
       <c r="H42" t="n">
-        <v>4244.382463</v>
+        <v>4244.285773</v>
       </c>
       <c r="I42" t="n">
-        <v>5203.401287</v>
+        <v>5203.058255</v>
       </c>
       <c r="J42" t="n">
         <v>147875.509146</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>774.764056</v>
+        <v>774.764139</v>
       </c>
       <c r="F43" t="n">
-        <v>1606.470564</v>
+        <v>1606.470993</v>
       </c>
       <c r="G43" t="n">
-        <v>2801.886186</v>
+        <v>2801.887551</v>
       </c>
       <c r="H43" t="n">
-        <v>4378.478812</v>
+        <v>4378.482878</v>
       </c>
       <c r="I43" t="n">
-        <v>6373.167107</v>
+        <v>6373.183154</v>
       </c>
       <c r="J43" t="n">
         <v>1428.397866</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4446.648423</v>
+        <v>4446.648823</v>
       </c>
       <c r="F44" t="n">
-        <v>7369.257253</v>
+        <v>7369.258908</v>
       </c>
       <c r="G44" t="n">
-        <v>10702.830698</v>
+        <v>10702.834969</v>
       </c>
       <c r="H44" t="n">
-        <v>14759.093429</v>
+        <v>14759.104307</v>
       </c>
       <c r="I44" t="n">
-        <v>19825.160942</v>
+        <v>19825.199652</v>
       </c>
       <c r="J44" t="n">
         <v>9330.732717999999</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>534.04306</v>
+        <v>534.043056</v>
       </c>
       <c r="F45" t="n">
-        <v>892.365938</v>
+        <v>892.365874</v>
       </c>
       <c r="G45" t="n">
-        <v>1268.686173</v>
+        <v>1268.685807</v>
       </c>
       <c r="H45" t="n">
-        <v>1665.553497</v>
+        <v>1665.552086</v>
       </c>
       <c r="I45" t="n">
-        <v>2120.034546</v>
+        <v>2120.028492</v>
       </c>
       <c r="J45" t="n">
         <v>5478.567282</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14.834606</v>
+        <v>14.834587</v>
       </c>
       <c r="F46" t="n">
-        <v>24.160224</v>
+        <v>24.160143</v>
       </c>
       <c r="G46" t="n">
-        <v>35.737677</v>
+        <v>35.73741</v>
       </c>
       <c r="H46" t="n">
-        <v>51.408581</v>
+        <v>51.40768</v>
       </c>
       <c r="I46" t="n">
-        <v>75.88585500000001</v>
+        <v>75.88146399999999</v>
       </c>
       <c r="J46" t="n">
         <v>2674.742729</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23879.90044</v>
+        <v>23879.896121</v>
       </c>
       <c r="F47" t="n">
-        <v>43452.501477</v>
+        <v>43452.473013</v>
       </c>
       <c r="G47" t="n">
-        <v>64384.833783</v>
+        <v>64384.725991</v>
       </c>
       <c r="H47" t="n">
-        <v>88250.68951700001</v>
+        <v>88250.328095</v>
       </c>
       <c r="I47" t="n">
-        <v>118227.6078</v>
+        <v>118226.076214</v>
       </c>
       <c r="J47" t="n">
         <v>901476.180983</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>285.565203</v>
+        <v>285.565075</v>
       </c>
       <c r="F48" t="n">
-        <v>447.902981</v>
+        <v>447.902436</v>
       </c>
       <c r="G48" t="n">
-        <v>616.896015</v>
+        <v>616.894337</v>
       </c>
       <c r="H48" t="n">
-        <v>797.4911540000001</v>
+        <v>797.486261</v>
       </c>
       <c r="I48" t="n">
-        <v>1001.783201</v>
+        <v>1001.765087</v>
       </c>
       <c r="J48" t="n">
         <v>8846.410978</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1050.789767</v>
+        <v>1050.789849</v>
       </c>
       <c r="F49" t="n">
-        <v>1746.547726</v>
+        <v>1746.548055</v>
       </c>
       <c r="G49" t="n">
-        <v>2448.668871</v>
+        <v>2448.669648</v>
       </c>
       <c r="H49" t="n">
-        <v>3166.457304</v>
+        <v>3166.459088</v>
       </c>
       <c r="I49" t="n">
-        <v>3946.663523</v>
+        <v>3946.669392</v>
       </c>
       <c r="J49" t="n">
         <v>2429.252122</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>28.057255</v>
+        <v>28.057254</v>
       </c>
       <c r="F50" t="n">
-        <v>43.677541</v>
+        <v>43.677536</v>
       </c>
       <c r="G50" t="n">
-        <v>56.179816</v>
+        <v>56.179798</v>
       </c>
       <c r="H50" t="n">
-        <v>66.857868</v>
+        <v>66.857814</v>
       </c>
       <c r="I50" t="n">
-        <v>77.678301</v>
+        <v>77.678113</v>
       </c>
       <c r="J50" t="n">
         <v>164.330855</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.000507</v>
+        <v>0.000382</v>
       </c>
       <c r="F51" t="n">
-        <v>0.001902</v>
+        <v>0.001433</v>
       </c>
       <c r="G51" t="n">
-        <v>0.005251</v>
+        <v>0.003956</v>
       </c>
       <c r="H51" t="n">
-        <v>0.014484</v>
+        <v>0.010911</v>
       </c>
       <c r="I51" t="n">
-        <v>0.053528</v>
+        <v>0.040324</v>
       </c>
       <c r="J51" t="n">
         <v>5733.625062</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>211.39199</v>
+        <v>211.392002</v>
       </c>
       <c r="F52" t="n">
-        <v>285.524836</v>
+        <v>285.524879</v>
       </c>
       <c r="G52" t="n">
-        <v>346.635821</v>
+        <v>346.635917</v>
       </c>
       <c r="H52" t="n">
-        <v>414.060196</v>
+        <v>414.06041</v>
       </c>
       <c r="I52" t="n">
-        <v>499.464661</v>
+        <v>499.46535</v>
       </c>
       <c r="J52" t="n">
         <v>332.651521</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112517.970162</v>
+        <v>112515.263145</v>
       </c>
       <c r="F54" t="n">
-        <v>159833.7503</v>
+        <v>159824.184525</v>
       </c>
       <c r="G54" t="n">
-        <v>237289.869278</v>
+        <v>237261.493314</v>
       </c>
       <c r="H54" t="n">
-        <v>331985.831612</v>
+        <v>331906.517539</v>
       </c>
       <c r="I54" t="n">
-        <v>434086.828483</v>
+        <v>433828.385876</v>
       </c>
       <c r="J54" t="n">
         <v>925408.566808</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>121035.955438</v>
+        <v>121038.662455</v>
       </c>
       <c r="F55" t="n">
-        <v>159735.11625</v>
+        <v>159744.682025</v>
       </c>
       <c r="G55" t="n">
-        <v>223598.006722</v>
+        <v>223626.382686</v>
       </c>
       <c r="H55" t="n">
-        <v>298874.032788</v>
+        <v>298953.346861</v>
       </c>
       <c r="I55" t="n">
-        <v>376836.857117</v>
+        <v>377095.299724</v>
       </c>
       <c r="J55" t="n">
         <v>79583.05379200001</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.016863</v>
+        <v>0.008954999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.093525</v>
+        <v>0.049666</v>
       </c>
       <c r="G58" t="n">
-        <v>0.337467</v>
+        <v>0.179211</v>
       </c>
       <c r="H58" t="n">
-        <v>1.064214</v>
+        <v>0.565153</v>
       </c>
       <c r="I58" t="n">
-        <v>3.950209</v>
+        <v>2.097826</v>
       </c>
       <c r="J58" t="n">
         <v>55982.98263</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.001332</v>
+        <v>0.0007069999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00775</v>
+        <v>0.004115</v>
       </c>
       <c r="G59" t="n">
-        <v>0.029143</v>
+        <v>0.015476</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09160799999999999</v>
+        <v>0.048649</v>
       </c>
       <c r="I59" t="n">
-        <v>0.333742</v>
+        <v>0.177239</v>
       </c>
       <c r="J59" t="n">
         <v>4651.284602</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.006358</v>
+        <v>0.003377</v>
       </c>
       <c r="F60" t="n">
-        <v>0.024816</v>
+        <v>0.013178</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06276</v>
+        <v>0.033329</v>
       </c>
       <c r="H60" t="n">
-        <v>0.153501</v>
+        <v>0.08151700000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>0.487317</v>
+        <v>0.258798</v>
       </c>
       <c r="J60" t="n">
         <v>6343.99599</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38316.833956</v>
+        <v>38316.875754</v>
       </c>
       <c r="F61" t="n">
-        <v>80848.20493599999</v>
+        <v>80848.433334</v>
       </c>
       <c r="G61" t="n">
-        <v>129088.367511</v>
+        <v>129089.109311</v>
       </c>
       <c r="H61" t="n">
-        <v>176524.346386</v>
+        <v>176526.451371</v>
       </c>
       <c r="I61" t="n">
-        <v>226259.627243</v>
+        <v>226266.709094</v>
       </c>
       <c r="J61" t="n">
         <v>79071.151257</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2867.428722</v>
+        <v>2867.380458</v>
       </c>
       <c r="F62" t="n">
-        <v>6464.067776</v>
+        <v>6463.737632</v>
       </c>
       <c r="G62" t="n">
-        <v>10711.956025</v>
+        <v>10710.71286</v>
       </c>
       <c r="H62" t="n">
-        <v>14702.323576</v>
+        <v>14698.571696</v>
       </c>
       <c r="I62" t="n">
-        <v>18446.828185</v>
+        <v>18434.032524</v>
       </c>
       <c r="J62" t="n">
         <v>373979.298096</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4800.409525</v>
+        <v>4800.383689</v>
       </c>
       <c r="F63" t="n">
-        <v>10511.478074</v>
+        <v>10511.32098</v>
       </c>
       <c r="G63" t="n">
-        <v>16813.340037</v>
+        <v>16812.823267</v>
       </c>
       <c r="H63" t="n">
-        <v>22935.103684</v>
+        <v>22933.652837</v>
       </c>
       <c r="I63" t="n">
-        <v>29514.207487</v>
+        <v>29509.267106</v>
       </c>
       <c r="J63" t="n">
         <v>181354.661298</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0007649999999999999</v>
+        <v>0.000406</v>
       </c>
       <c r="F64" t="n">
-        <v>0.003681</v>
+        <v>0.001955</v>
       </c>
       <c r="G64" t="n">
-        <v>0.011519</v>
+        <v>0.006117</v>
       </c>
       <c r="H64" t="n">
-        <v>0.032196</v>
+        <v>0.017098</v>
       </c>
       <c r="I64" t="n">
-        <v>0.10943</v>
+        <v>0.058115</v>
       </c>
       <c r="J64" t="n">
         <v>1462.680712</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>24280.466907</v>
+        <v>24280.487733</v>
       </c>
       <c r="F65" t="n">
-        <v>55599.426016</v>
+        <v>55599.546755</v>
       </c>
       <c r="G65" t="n">
-        <v>97990.357156</v>
+        <v>97990.77602999999</v>
       </c>
       <c r="H65" t="n">
-        <v>148046.998312</v>
+        <v>148048.274535</v>
       </c>
       <c r="I65" t="n">
-        <v>208700.659171</v>
+        <v>208705.23987</v>
       </c>
       <c r="J65" t="n">
         <v>142963.762115</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14343.747265</v>
+        <v>14343.766545</v>
       </c>
       <c r="F66" t="n">
-        <v>32050.131793</v>
+        <v>32050.24295</v>
       </c>
       <c r="G66" t="n">
-        <v>55168.315014</v>
+        <v>55168.701105</v>
       </c>
       <c r="H66" t="n">
-        <v>81430.047209</v>
+        <v>81431.217966</v>
       </c>
       <c r="I66" t="n">
-        <v>112233.428995</v>
+        <v>112237.628186</v>
       </c>
       <c r="J66" t="n">
         <v>22014.377043</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>307.852843</v>
+        <v>307.85278</v>
       </c>
       <c r="F67" t="n">
-        <v>703.575551</v>
+        <v>703.57488</v>
       </c>
       <c r="G67" t="n">
-        <v>1267.758545</v>
+        <v>1267.754461</v>
       </c>
       <c r="H67" t="n">
-        <v>1956.282463</v>
+        <v>1956.264344</v>
       </c>
       <c r="I67" t="n">
-        <v>2801.225842</v>
+        <v>2801.138008</v>
       </c>
       <c r="J67" t="n">
         <v>7127.061724</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1016.639698</v>
+        <v>1016.63509</v>
       </c>
       <c r="F68" t="n">
-        <v>2360.885195</v>
+        <v>2360.851235</v>
       </c>
       <c r="G68" t="n">
-        <v>4382.845913</v>
+        <v>4382.680844</v>
       </c>
       <c r="H68" t="n">
-        <v>6719.285103</v>
+        <v>6718.654942</v>
       </c>
       <c r="I68" t="n">
-        <v>9172.857724</v>
+        <v>9170.310857</v>
       </c>
       <c r="J68" t="n">
         <v>89259.548681</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.001808</v>
+        <v>0.00096</v>
       </c>
       <c r="F69" t="n">
-        <v>0.009971000000000001</v>
+        <v>0.005295</v>
       </c>
       <c r="G69" t="n">
-        <v>0.033393</v>
+        <v>0.017734</v>
       </c>
       <c r="H69" t="n">
-        <v>0.09587900000000001</v>
+        <v>0.050917</v>
       </c>
       <c r="I69" t="n">
-        <v>0.328497</v>
+        <v>0.174454</v>
       </c>
       <c r="J69" t="n">
         <v>4491.229659</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8215.346136</v>
+        <v>8215.358115999999</v>
       </c>
       <c r="F70" t="n">
-        <v>17686.113879</v>
+        <v>17686.180499</v>
       </c>
       <c r="G70" t="n">
-        <v>29401.692073</v>
+        <v>29401.91589</v>
       </c>
       <c r="H70" t="n">
-        <v>41645.960883</v>
+        <v>41646.612699</v>
       </c>
       <c r="I70" t="n">
-        <v>55041.605052</v>
+        <v>55043.849289</v>
       </c>
       <c r="J70" t="n">
         <v>5063.335954</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>24073.317174</v>
+        <v>24073.339988</v>
       </c>
       <c r="F71" t="n">
-        <v>56922.282401</v>
+        <v>56922.410696</v>
       </c>
       <c r="G71" t="n">
-        <v>95404.228408</v>
+        <v>95404.64887999999</v>
       </c>
       <c r="H71" t="n">
-        <v>132119.954073</v>
+        <v>132121.155645</v>
       </c>
       <c r="I71" t="n">
-        <v>168836.223926</v>
+        <v>168840.276634</v>
       </c>
       <c r="J71" t="n">
         <v>92793.50891800001</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12646.990635</v>
+        <v>12647.003844</v>
       </c>
       <c r="F72" t="n">
-        <v>25156.435944</v>
+        <v>25156.504162</v>
       </c>
       <c r="G72" t="n">
-        <v>38934.368846</v>
+        <v>38934.581075</v>
       </c>
       <c r="H72" t="n">
-        <v>52176.621929</v>
+        <v>52177.202232</v>
       </c>
       <c r="I72" t="n">
-        <v>66363.93767100001</v>
+        <v>66365.82997999999</v>
       </c>
       <c r="J72" t="n">
         <v>29742.661035</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21.559467</v>
+        <v>21.521308</v>
       </c>
       <c r="F73" t="n">
-        <v>35.743906</v>
+        <v>35.609798</v>
       </c>
       <c r="G73" t="n">
-        <v>42.180136</v>
+        <v>41.935464</v>
       </c>
       <c r="H73" t="n">
-        <v>45.686511</v>
+        <v>45.246359</v>
       </c>
       <c r="I73" t="n">
-        <v>52.528158</v>
+        <v>51.358406</v>
       </c>
       <c r="J73" t="n">
         <v>30391.819745</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.000545</v>
+        <v>0.00029</v>
       </c>
       <c r="F74" t="n">
-        <v>0.004089</v>
+        <v>0.002171</v>
       </c>
       <c r="G74" t="n">
-        <v>0.015151</v>
+        <v>0.008045999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.043575</v>
+        <v>0.023141</v>
       </c>
       <c r="I74" t="n">
-        <v>0.144451</v>
+        <v>0.076713</v>
       </c>
       <c r="J74" t="n">
         <v>1881.81864</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7991.614238</v>
+        <v>7991.642142</v>
       </c>
       <c r="F75" t="n">
-        <v>9234.850011</v>
+        <v>9234.863856</v>
       </c>
       <c r="G75" t="n">
-        <v>10932.924739</v>
+        <v>10932.757529</v>
       </c>
       <c r="H75" t="n">
-        <v>13555.995954</v>
+        <v>13555.282475</v>
       </c>
       <c r="I75" t="n">
-        <v>15868.705213</v>
+        <v>15866.163712</v>
       </c>
       <c r="J75" t="n">
         <v>28238.596847</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6295.023714</v>
+        <v>6294.08594</v>
       </c>
       <c r="F76" t="n">
-        <v>7512.391897</v>
+        <v>7509.298129</v>
       </c>
       <c r="G76" t="n">
-        <v>7285.033664</v>
+        <v>7278.855912</v>
       </c>
       <c r="H76" t="n">
-        <v>7725.488716</v>
+        <v>7712.448077</v>
       </c>
       <c r="I76" t="n">
-        <v>8512.369178000001</v>
+        <v>8477.582957000001</v>
       </c>
       <c r="J76" t="n">
         <v>136912.472528</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30567.521067</v>
+        <v>30567.920495</v>
       </c>
       <c r="F77" t="n">
-        <v>40105.607922</v>
+        <v>40106.698687</v>
       </c>
       <c r="G77" t="n">
-        <v>49831.859251</v>
+        <v>49833.827677</v>
       </c>
       <c r="H77" t="n">
-        <v>60062.714301</v>
+        <v>60066.424019</v>
       </c>
       <c r="I77" t="n">
-        <v>65151.855315</v>
+        <v>65160.534742</v>
       </c>
       <c r="J77" t="n">
         <v>40213.292861</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34444.144348</v>
+        <v>34443.253126</v>
       </c>
       <c r="F78" t="n">
-        <v>34591.779041</v>
+        <v>34589.230094</v>
       </c>
       <c r="G78" t="n">
-        <v>34766.092717</v>
+        <v>34760.345884</v>
       </c>
       <c r="H78" t="n">
-        <v>39057.050301</v>
+        <v>39043.422552</v>
       </c>
       <c r="I78" t="n">
-        <v>44272.840992</v>
+        <v>44233.559346</v>
       </c>
       <c r="J78" t="n">
         <v>199103.107763</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>40133.27939</v>
+        <v>40133.945406</v>
       </c>
       <c r="F79" t="n">
-        <v>60665.346047</v>
+        <v>60667.59452</v>
       </c>
       <c r="G79" t="n">
-        <v>93853.725278</v>
+        <v>93859.410406</v>
       </c>
       <c r="H79" t="n">
-        <v>143079.637678</v>
+        <v>143094.586688</v>
       </c>
       <c r="I79" t="n">
-        <v>192854.303446</v>
+        <v>192900.204411</v>
       </c>
       <c r="J79" t="n">
         <v>61460.377439</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>799.51959</v>
+        <v>799.488733</v>
       </c>
       <c r="F80" t="n">
-        <v>788.359951</v>
+        <v>788.27658</v>
       </c>
       <c r="G80" t="n">
-        <v>808.44943</v>
+        <v>808.2624080000001</v>
       </c>
       <c r="H80" t="n">
-        <v>952.612318</v>
+        <v>952.148668</v>
       </c>
       <c r="I80" t="n">
-        <v>1141.720273</v>
+        <v>1140.301401</v>
       </c>
       <c r="J80" t="n">
         <v>7068.868805</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>61465.031975</v>
+        <v>61466.084962</v>
       </c>
       <c r="F81" t="n">
-        <v>96471.05924800001</v>
+        <v>96474.78178999999</v>
       </c>
       <c r="G81" t="n">
-        <v>152661.903834</v>
+        <v>152671.678469</v>
       </c>
       <c r="H81" t="n">
-        <v>238747.585941</v>
+        <v>238774.317997</v>
       </c>
       <c r="I81" t="n">
-        <v>332049.136945</v>
+        <v>332134.630886</v>
       </c>
       <c r="J81" t="n">
         <v>81894.414932</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>13.619012</v>
+        <v>13.35876</v>
       </c>
       <c r="F82" t="n">
-        <v>21.3494</v>
+        <v>20.53012</v>
       </c>
       <c r="G82" t="n">
-        <v>35.808401</v>
+        <v>33.812644</v>
       </c>
       <c r="H82" t="n">
-        <v>73.049869</v>
+        <v>67.900048</v>
       </c>
       <c r="I82" t="n">
-        <v>190.326793</v>
+        <v>174.551735</v>
       </c>
       <c r="J82" t="n">
         <v>62085.949759</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24681.181666</v>
+        <v>24681.155435</v>
       </c>
       <c r="F83" t="n">
-        <v>38225.951486</v>
+        <v>38225.421229</v>
       </c>
       <c r="G83" t="n">
-        <v>58413.871694</v>
+        <v>58410.718078</v>
       </c>
       <c r="H83" t="n">
-        <v>87412.63415500001</v>
+        <v>87400.238708</v>
       </c>
       <c r="I83" t="n">
-        <v>115885.518747</v>
+        <v>115839.247714</v>
       </c>
       <c r="J83" t="n">
         <v>337059.064863</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>28444.045634</v>
+        <v>28444.314993</v>
       </c>
       <c r="F86" t="n">
-        <v>37070.60847</v>
+        <v>37071.523733</v>
       </c>
       <c r="G86" t="n">
-        <v>49255.95358</v>
+        <v>49258.480795</v>
       </c>
       <c r="H86" t="n">
-        <v>65463.948549</v>
+        <v>65470.891696</v>
       </c>
       <c r="I86" t="n">
-        <v>81684.516466</v>
+        <v>81706.75851</v>
       </c>
       <c r="J86" t="n">
         <v>43453.662061</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1297.320118</v>
+        <v>1297.273104</v>
       </c>
       <c r="F87" t="n">
-        <v>1902.411081</v>
+        <v>1902.226661</v>
       </c>
       <c r="G87" t="n">
-        <v>2906.74576</v>
+        <v>2906.146772</v>
       </c>
       <c r="H87" t="n">
-        <v>4347.697387</v>
+        <v>4345.835764</v>
       </c>
       <c r="I87" t="n">
-        <v>5976.581075</v>
+        <v>5970.051445</v>
       </c>
       <c r="J87" t="n">
         <v>24473.09179</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>30591.93606</v>
+        <v>30591.739561</v>
       </c>
       <c r="F88" t="n">
-        <v>36332.46474</v>
+        <v>36331.945347</v>
       </c>
       <c r="G88" t="n">
-        <v>45527.790918</v>
+        <v>45526.637769</v>
       </c>
       <c r="H88" t="n">
-        <v>60040.732567</v>
+        <v>60037.922584</v>
       </c>
       <c r="I88" t="n">
-        <v>76806.516214</v>
+        <v>76797.82821000001</v>
       </c>
       <c r="J88" t="n">
         <v>116506.235585</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5064.888501</v>
+        <v>5064.913079</v>
       </c>
       <c r="F89" t="n">
-        <v>6386.049563</v>
+        <v>6386.133335</v>
       </c>
       <c r="G89" t="n">
-        <v>8615.199834999999</v>
+        <v>8615.435681000001</v>
       </c>
       <c r="H89" t="n">
-        <v>11693.992197</v>
+        <v>11694.656482</v>
       </c>
       <c r="I89" t="n">
-        <v>14925.848951</v>
+        <v>14928.031942</v>
       </c>
       <c r="J89" t="n">
         <v>12740.416859</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10482.604038</v>
+        <v>10482.32554</v>
       </c>
       <c r="F90" t="n">
-        <v>13377.550215</v>
+        <v>13376.631839</v>
       </c>
       <c r="G90" t="n">
-        <v>18423.842703</v>
+        <v>18421.202544</v>
       </c>
       <c r="H90" t="n">
-        <v>25739.447733</v>
+        <v>25731.811254</v>
       </c>
       <c r="I90" t="n">
-        <v>33707.712147</v>
+        <v>33682.083051</v>
       </c>
       <c r="J90" t="n">
         <v>105531.155955</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5448.277363</v>
+        <v>5448.231157</v>
       </c>
       <c r="F91" t="n">
-        <v>7107.841628</v>
+        <v>7107.682526</v>
       </c>
       <c r="G91" t="n">
-        <v>9560.552328</v>
+        <v>9560.108340999999</v>
       </c>
       <c r="H91" t="n">
-        <v>12656.784972</v>
+        <v>12655.606923</v>
       </c>
       <c r="I91" t="n">
-        <v>15516.077897</v>
+        <v>15512.531681</v>
       </c>
       <c r="J91" t="n">
         <v>25848.946677</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9015.134808999999</v>
+        <v>9015.211047000001</v>
       </c>
       <c r="F92" t="n">
-        <v>11860.926413</v>
+        <v>11861.186762</v>
       </c>
       <c r="G92" t="n">
-        <v>16467.929502</v>
+        <v>16468.66906</v>
       </c>
       <c r="H92" t="n">
-        <v>22404.951436</v>
+        <v>22407.014967</v>
       </c>
       <c r="I92" t="n">
-        <v>28098.154692</v>
+        <v>28104.788187</v>
       </c>
       <c r="J92" t="n">
         <v>17273.966883</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>331.226117</v>
+        <v>331.203255</v>
       </c>
       <c r="F93" t="n">
-        <v>458.240386</v>
+        <v>458.156743</v>
       </c>
       <c r="G93" t="n">
-        <v>678.055782</v>
+        <v>677.7932489999999</v>
       </c>
       <c r="H93" t="n">
-        <v>1011.240115</v>
+        <v>1010.418017</v>
       </c>
       <c r="I93" t="n">
-        <v>1400.419148</v>
+        <v>1397.474859</v>
       </c>
       <c r="J93" t="n">
         <v>9487.340531</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>73649.67767999999</v>
+        <v>73648.914202</v>
       </c>
       <c r="F94" t="n">
-        <v>103164.633936</v>
+        <v>103161.693874</v>
       </c>
       <c r="G94" t="n">
-        <v>145205.1164</v>
+        <v>145196.342232</v>
       </c>
       <c r="H94" t="n">
-        <v>201057.585694</v>
+        <v>201032.573107</v>
       </c>
       <c r="I94" t="n">
-        <v>257723.113234</v>
+        <v>257641.923989</v>
       </c>
       <c r="J94" t="n">
         <v>507807.072</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>85068.831267</v>
+        <v>85069.722719</v>
       </c>
       <c r="F95" t="n">
-        <v>119363.969746</v>
+        <v>119367.188061</v>
       </c>
       <c r="G95" t="n">
-        <v>170662.731813</v>
+        <v>170672.140172</v>
       </c>
       <c r="H95" t="n">
-        <v>238688.973694</v>
+        <v>238715.825975</v>
       </c>
       <c r="I95" t="n">
-        <v>307790.892087</v>
+        <v>307878.941546</v>
       </c>
       <c r="J95" t="n">
         <v>157238.713287</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>19610.587209</v>
+        <v>19610.582731</v>
       </c>
       <c r="F96" t="n">
-        <v>24344.339945</v>
+        <v>24344.352432</v>
       </c>
       <c r="G96" t="n">
-        <v>30714.417925</v>
+        <v>30714.536925</v>
       </c>
       <c r="H96" t="n">
-        <v>40166.850409</v>
+        <v>40167.327308</v>
       </c>
       <c r="I96" t="n">
-        <v>50606.375981</v>
+        <v>50608.172797</v>
       </c>
       <c r="J96" t="n">
         <v>56993.215778</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14139.371204</v>
+        <v>14139.468611</v>
       </c>
       <c r="F97" t="n">
-        <v>16246.996578</v>
+        <v>16247.311387</v>
       </c>
       <c r="G97" t="n">
-        <v>19913.851655</v>
+        <v>19914.694659</v>
       </c>
       <c r="H97" t="n">
-        <v>25920.539347</v>
+        <v>25922.860024</v>
       </c>
       <c r="I97" t="n">
-        <v>32958.120209</v>
+        <v>32965.741882</v>
       </c>
       <c r="J97" t="n">
         <v>21671.552694</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>157670.800759</v>
+        <v>157673.328748</v>
       </c>
       <c r="F98" t="n">
-        <v>177524.404817</v>
+        <v>177531.843257</v>
       </c>
       <c r="G98" t="n">
-        <v>205365.791333</v>
+        <v>205383.8863</v>
       </c>
       <c r="H98" t="n">
-        <v>236753.222569</v>
+        <v>236796.758274</v>
       </c>
       <c r="I98" t="n">
-        <v>269682.673268</v>
+        <v>269810.768797</v>
       </c>
       <c r="J98" t="n">
         <v>121784.254056</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>47901.097826</v>
+        <v>47899.88937</v>
       </c>
       <c r="F99" t="n">
-        <v>62432.586626</v>
+        <v>62428.515671</v>
       </c>
       <c r="G99" t="n">
-        <v>84611.17658</v>
+        <v>84599.769077</v>
       </c>
       <c r="H99" t="n">
-        <v>110097.848221</v>
+        <v>110067.434769</v>
       </c>
       <c r="I99" t="n">
-        <v>136562.050956</v>
+        <v>136466.440864</v>
       </c>
       <c r="J99" t="n">
         <v>302968.330171</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>62752.172318</v>
+        <v>62752.8316</v>
       </c>
       <c r="F100" t="n">
-        <v>70141.26192400001</v>
+        <v>70143.233792</v>
       </c>
       <c r="G100" t="n">
-        <v>82176.841652</v>
+        <v>82181.795875</v>
       </c>
       <c r="H100" t="n">
-        <v>96025.716396</v>
+        <v>96037.97613700001</v>
       </c>
       <c r="I100" t="n">
-        <v>110621.252344</v>
+        <v>110658.112984</v>
       </c>
       <c r="J100" t="n">
         <v>72337.12878299999</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101155.608798</v>
+        <v>101157.392526</v>
       </c>
       <c r="F101" t="n">
-        <v>121182.073314</v>
+        <v>121187.6029</v>
       </c>
       <c r="G101" t="n">
-        <v>150950.373293</v>
+        <v>150964.695084</v>
       </c>
       <c r="H101" t="n">
-        <v>183972.989744</v>
+        <v>184009.115781</v>
       </c>
       <c r="I101" t="n">
-        <v>217060.332133</v>
+        <v>217169.849368</v>
       </c>
       <c r="J101" t="n">
         <v>91112.96197</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>305760.271355</v>
+        <v>305756.242528</v>
       </c>
       <c r="F102" t="n">
-        <v>387443.064029</v>
+        <v>387430.085151</v>
       </c>
       <c r="G102" t="n">
-        <v>515991.939335</v>
+        <v>515956.631363</v>
       </c>
       <c r="H102" t="n">
-        <v>668971.284964</v>
+        <v>668878.1035119999</v>
       </c>
       <c r="I102" t="n">
-        <v>833895.860057</v>
+        <v>833602.1948159999</v>
       </c>
       <c r="J102" t="n">
         <v>1435160.229327</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>625599.985372</v>
+        <v>625602.11814</v>
       </c>
       <c r="F103" t="n">
-        <v>678872.205972</v>
+        <v>678879.266087</v>
       </c>
       <c r="G103" t="n">
-        <v>763773.81586</v>
+        <v>763792.947807</v>
       </c>
       <c r="H103" t="n">
-        <v>862312.645426</v>
+        <v>862362.018234</v>
       </c>
       <c r="I103" t="n">
-        <v>968197.221226</v>
+        <v>968348.824453</v>
       </c>
       <c r="J103" t="n">
         <v>856612.670877</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>49212.643374</v>
+        <v>49212.038507</v>
       </c>
       <c r="F104" t="n">
-        <v>59933.478222</v>
+        <v>59931.61808</v>
       </c>
       <c r="G104" t="n">
-        <v>76129.92026499999</v>
+        <v>76125.151643</v>
       </c>
       <c r="H104" t="n">
-        <v>95779.633959</v>
+        <v>95767.458824</v>
       </c>
       <c r="I104" t="n">
-        <v>117148.732407</v>
+        <v>117110.994094</v>
       </c>
       <c r="J104" t="n">
         <v>194075.024572</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26407.678766</v>
+        <v>26407.419566</v>
       </c>
       <c r="F105" t="n">
-        <v>32683.167346</v>
+        <v>32682.381534</v>
       </c>
       <c r="G105" t="n">
-        <v>42687.525671</v>
+        <v>42685.493415</v>
       </c>
       <c r="H105" t="n">
-        <v>54254.121741</v>
+        <v>54249.018358</v>
       </c>
       <c r="I105" t="n">
-        <v>66415.47719000001</v>
+        <v>66400.11962699999</v>
       </c>
       <c r="J105" t="n">
         <v>100213.020163</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>360893.939723</v>
+        <v>360893.577434</v>
       </c>
       <c r="F106" t="n">
-        <v>460906.286697</v>
+        <v>460905.008793</v>
       </c>
       <c r="G106" t="n">
-        <v>623982.8621659999</v>
+        <v>623978.8652229999</v>
       </c>
       <c r="H106" t="n">
-        <v>814925.634524</v>
+        <v>814914.2182229999</v>
       </c>
       <c r="I106" t="n">
-        <v>1014643.127235</v>
+        <v>1014605.930734</v>
       </c>
       <c r="J106" t="n">
         <v>1262393.265333</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1428.772184</v>
+        <v>1428.416604</v>
       </c>
       <c r="F107" t="n">
-        <v>1924.663679</v>
+        <v>1923.434883</v>
       </c>
       <c r="G107" t="n">
-        <v>2556.958242</v>
+        <v>2553.640299</v>
       </c>
       <c r="H107" t="n">
-        <v>3289.371507</v>
+        <v>3280.756626</v>
       </c>
       <c r="I107" t="n">
-        <v>4139.00915</v>
+        <v>4112.012341</v>
       </c>
       <c r="J107" t="n">
         <v>45461.233655</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>45371.381128</v>
+        <v>45368.017731</v>
       </c>
       <c r="F108" t="n">
-        <v>55131.984679</v>
+        <v>55121.622569</v>
       </c>
       <c r="G108" t="n">
-        <v>68661.06295399999</v>
+        <v>68634.96339600001</v>
       </c>
       <c r="H108" t="n">
-        <v>83699.254521</v>
+        <v>83635.100416</v>
       </c>
       <c r="I108" t="n">
-        <v>99279.88918100001</v>
+        <v>99089.22704</v>
       </c>
       <c r="J108" t="n">
         <v>385224.327085</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>80759.967561</v>
+        <v>80761.027027</v>
       </c>
       <c r="F109" t="n">
-        <v>98382.51197799999</v>
+        <v>98385.85453</v>
       </c>
       <c r="G109" t="n">
-        <v>130801.564907</v>
+        <v>130810.728792</v>
       </c>
       <c r="H109" t="n">
-        <v>174438.285813</v>
+        <v>174463.238595</v>
       </c>
       <c r="I109" t="n">
-        <v>226751.357053</v>
+        <v>226833.405751</v>
       </c>
       <c r="J109" t="n">
         <v>155540.638139</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>339630.261179</v>
+        <v>339637.710464</v>
       </c>
       <c r="F110" t="n">
-        <v>439448.882863</v>
+        <v>439473.651158</v>
       </c>
       <c r="G110" t="n">
-        <v>595655.851541</v>
+        <v>595725.124537</v>
       </c>
       <c r="H110" t="n">
-        <v>775660.606471</v>
+        <v>775846.16827</v>
       </c>
       <c r="I110" t="n">
-        <v>959653.456881</v>
+        <v>960240.81557</v>
       </c>
       <c r="J110" t="n">
         <v>265898.09853</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>321733.507045</v>
+        <v>321734.221744</v>
       </c>
       <c r="F111" t="n">
-        <v>403255.791427</v>
+        <v>403258.194595</v>
       </c>
       <c r="G111" t="n">
-        <v>522215.920415</v>
+        <v>522222.786307</v>
       </c>
       <c r="H111" t="n">
-        <v>657690.446693</v>
+        <v>657709.388144</v>
       </c>
       <c r="I111" t="n">
-        <v>802402.553692</v>
+        <v>802464.483141</v>
       </c>
       <c r="J111" t="n">
         <v>853033.670258</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>276286.612612</v>
+        <v>276280.46801</v>
       </c>
       <c r="F112" t="n">
-        <v>351467.525427</v>
+        <v>351447.575998</v>
       </c>
       <c r="G112" t="n">
-        <v>470965.956784</v>
+        <v>470911.081882</v>
       </c>
       <c r="H112" t="n">
-        <v>612024.863452</v>
+        <v>611879.1718369999</v>
       </c>
       <c r="I112" t="n">
-        <v>762815.483227</v>
+        <v>762355.296421</v>
       </c>
       <c r="J112" t="n">
         <v>1596224.36308</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>980.965004</v>
+        <v>980.595749</v>
       </c>
       <c r="F113" t="n">
-        <v>1598.024724</v>
+        <v>1596.334723</v>
       </c>
       <c r="G113" t="n">
-        <v>2270.378388</v>
+        <v>2265.352985</v>
       </c>
       <c r="H113" t="n">
-        <v>3510.66758</v>
+        <v>3494.949984</v>
       </c>
       <c r="I113" t="n">
-        <v>4668.571777</v>
+        <v>4616.729839</v>
       </c>
       <c r="J113" t="n">
         <v>53226.181107</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1011.928012</v>
+        <v>1011.953361</v>
       </c>
       <c r="F114" t="n">
-        <v>2325.629234</v>
+        <v>2325.772079</v>
       </c>
       <c r="G114" t="n">
-        <v>4918.224709</v>
+        <v>4918.749618</v>
       </c>
       <c r="H114" t="n">
-        <v>9900.818609</v>
+        <v>9902.638212</v>
       </c>
       <c r="I114" t="n">
-        <v>14896.55983</v>
+        <v>14902.674059</v>
       </c>
       <c r="J114" t="n">
         <v>14088.957368</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25044.890984</v>
+        <v>25045.23489</v>
       </c>
       <c r="F115" t="n">
-        <v>46838.247423</v>
+        <v>46839.794578</v>
       </c>
       <c r="G115" t="n">
-        <v>83081.472773</v>
+        <v>83085.973266</v>
       </c>
       <c r="H115" t="n">
-        <v>151284.722181</v>
+        <v>151298.620174</v>
       </c>
       <c r="I115" t="n">
-        <v>219924.619163</v>
+        <v>219970.346872</v>
       </c>
       <c r="J115" t="n">
         <v>249243.531295</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20982.800047</v>
+        <v>20982.87691</v>
       </c>
       <c r="F116" t="n">
-        <v>22472.26439</v>
+        <v>22472.470936</v>
       </c>
       <c r="G116" t="n">
-        <v>26727.938212</v>
+        <v>26728.431966</v>
       </c>
       <c r="H116" t="n">
-        <v>33245.519932</v>
+        <v>33246.753122</v>
       </c>
       <c r="I116" t="n">
-        <v>38822.349038</v>
+        <v>38825.953084</v>
       </c>
       <c r="J116" t="n">
         <v>9595.023173</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19760.306458</v>
+        <v>19760.332038</v>
       </c>
       <c r="F117" t="n">
-        <v>26141.371739</v>
+        <v>26141.453777</v>
       </c>
       <c r="G117" t="n">
-        <v>34293.714587</v>
+        <v>34293.927649</v>
       </c>
       <c r="H117" t="n">
-        <v>44861.252385</v>
+        <v>44861.808167</v>
       </c>
       <c r="I117" t="n">
-        <v>53654.698572</v>
+        <v>53656.356379</v>
       </c>
       <c r="J117" t="n">
         <v>44765.244416</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>26736.054628</v>
+        <v>26736.037572</v>
       </c>
       <c r="F118" t="n">
-        <v>27977.665042</v>
+        <v>27977.619947</v>
       </c>
       <c r="G118" t="n">
-        <v>32321.673128</v>
+        <v>32321.569622</v>
       </c>
       <c r="H118" t="n">
-        <v>39269.219926</v>
+        <v>39268.971625</v>
       </c>
       <c r="I118" t="n">
-        <v>45167.202297</v>
+        <v>45166.500962</v>
       </c>
       <c r="J118" t="n">
         <v>56292.555329</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>7223.237396</v>
+        <v>7223.235801</v>
       </c>
       <c r="F119" t="n">
-        <v>9124.784093</v>
+        <v>9124.777984</v>
       </c>
       <c r="G119" t="n">
-        <v>12533.292383</v>
+        <v>12533.273537</v>
       </c>
       <c r="H119" t="n">
-        <v>17409.988536</v>
+        <v>17409.932715</v>
       </c>
       <c r="I119" t="n">
-        <v>22029.610172</v>
+        <v>22029.428974</v>
       </c>
       <c r="J119" t="n">
         <v>27873.334529</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5307.395354</v>
+        <v>5307.407701</v>
       </c>
       <c r="F120" t="n">
-        <v>5722.195661</v>
+        <v>5722.22903</v>
       </c>
       <c r="G120" t="n">
-        <v>6866.449397</v>
+        <v>6866.529897</v>
       </c>
       <c r="H120" t="n">
-        <v>8638.521847</v>
+        <v>8638.725316</v>
       </c>
       <c r="I120" t="n">
-        <v>10227.824427</v>
+        <v>10228.427418</v>
       </c>
       <c r="J120" t="n">
         <v>5864.242658</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>36006.16324</v>
+        <v>36006.147298</v>
       </c>
       <c r="F121" t="n">
-        <v>44842.428839</v>
+        <v>44842.373441</v>
       </c>
       <c r="G121" t="n">
-        <v>60582.896792</v>
+        <v>60582.736379</v>
       </c>
       <c r="H121" t="n">
-        <v>82010.702796</v>
+        <v>82010.253442</v>
       </c>
       <c r="I121" t="n">
-        <v>100583.571032</v>
+        <v>100582.183776</v>
       </c>
       <c r="J121" t="n">
         <v>128506.005129</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>297822.973878</v>
+        <v>297822.893679</v>
       </c>
       <c r="F122" t="n">
-        <v>322337.274276</v>
+        <v>322337.058924</v>
       </c>
       <c r="G122" t="n">
-        <v>389438.985851</v>
+        <v>389438.481301</v>
       </c>
       <c r="H122" t="n">
-        <v>495492.963728</v>
+        <v>495491.724764</v>
       </c>
       <c r="I122" t="n">
-        <v>596423.273213</v>
+        <v>596419.678158</v>
       </c>
       <c r="J122" t="n">
         <v>722743.765515</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>66489.395252</v>
+        <v>66571.92413299999</v>
       </c>
       <c r="F123" t="n">
-        <v>71606.316578</v>
+        <v>71806.87134899999</v>
       </c>
       <c r="G123" t="n">
-        <v>79478.888756</v>
+        <v>79874.850884</v>
       </c>
       <c r="H123" t="n">
-        <v>86794.53120100001</v>
+        <v>87551.579453</v>
       </c>
       <c r="I123" t="n">
-        <v>88650.27679600001</v>
+        <v>90192.572363</v>
       </c>
       <c r="J123" t="n">
         <v>31427.012114</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>497954.733175</v>
+        <v>498301.435623</v>
       </c>
       <c r="F124" t="n">
-        <v>541650.4639410001</v>
+        <v>542491.276234</v>
       </c>
       <c r="G124" t="n">
-        <v>600208.0330159999</v>
+        <v>601829.558008</v>
       </c>
       <c r="H124" t="n">
-        <v>662536.729279</v>
+        <v>665581.599691</v>
       </c>
       <c r="I124" t="n">
-        <v>703063.178718</v>
+        <v>709140.166696</v>
       </c>
       <c r="J124" t="n">
         <v>510629.309035</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>150979.651573</v>
+        <v>150550.420244</v>
       </c>
       <c r="F125" t="n">
-        <v>158841.099551</v>
+        <v>157799.732487</v>
       </c>
       <c r="G125" t="n">
-        <v>172114.065498</v>
+        <v>170096.578378</v>
       </c>
       <c r="H125" t="n">
-        <v>198956.50699</v>
+        <v>195154.588326</v>
       </c>
       <c r="I125" t="n">
-        <v>258049.422956</v>
+        <v>250430.139411</v>
       </c>
       <c r="J125" t="n">
         <v>596032.968321</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1090.680365</v>
+        <v>1090.669586</v>
       </c>
       <c r="F130" t="n">
-        <v>10021.167215</v>
+        <v>10020.86835</v>
       </c>
       <c r="G130" t="n">
-        <v>18996.391075</v>
+        <v>18994.998636</v>
       </c>
       <c r="H130" t="n">
-        <v>31035.378911</v>
+        <v>31029.40461</v>
       </c>
       <c r="I130" t="n">
-        <v>46060.593929</v>
+        <v>46026.532913</v>
       </c>
       <c r="J130" t="n">
         <v>2252578.924047</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.00044</v>
+        <v>8.7e-05</v>
       </c>
       <c r="F131" t="n">
-        <v>0.01649</v>
+        <v>0.003247</v>
       </c>
       <c r="G131" t="n">
-        <v>0.08073</v>
+        <v>0.015894</v>
       </c>
       <c r="H131" t="n">
-        <v>0.340485</v>
+        <v>0.067034</v>
       </c>
       <c r="I131" t="n">
-        <v>1.879729</v>
+        <v>0.370084</v>
       </c>
       <c r="J131" t="n">
         <v>94953.24914</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>51229.14594</v>
+        <v>51229.159451</v>
       </c>
       <c r="F132" t="n">
-        <v>432417.269278</v>
+        <v>432417.58869</v>
       </c>
       <c r="G132" t="n">
-        <v>733941.791756</v>
+        <v>733943.068337</v>
       </c>
       <c r="H132" t="n">
-        <v>1071632.517595</v>
+        <v>1071637.443428</v>
       </c>
       <c r="I132" t="n">
-        <v>1440698.803792</v>
+        <v>1440725.11679</v>
       </c>
       <c r="J132" t="n">
         <v>176097.348771</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9308.213291</v>
+        <v>9308.215929</v>
       </c>
       <c r="F133" t="n">
-        <v>111952.770214</v>
+        <v>111952.856604</v>
       </c>
       <c r="G133" t="n">
-        <v>264160.60052</v>
+        <v>264161.059925</v>
       </c>
       <c r="H133" t="n">
-        <v>493072.339989</v>
+        <v>493074.533009</v>
       </c>
       <c r="I133" t="n">
-        <v>786650.478079</v>
+        <v>786664.185257</v>
       </c>
       <c r="J133" t="n">
         <v>154834.124717</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4342.410005</v>
+        <v>4342.409984</v>
       </c>
       <c r="F134" t="n">
-        <v>34675.605048</v>
+        <v>34675.607986</v>
       </c>
       <c r="G134" t="n">
-        <v>58238.477828</v>
+        <v>58238.501785</v>
       </c>
       <c r="H134" t="n">
-        <v>87181.69446</v>
+        <v>87181.829388</v>
       </c>
       <c r="I134" t="n">
-        <v>122424.98927</v>
+        <v>122425.90645</v>
       </c>
       <c r="J134" t="n">
         <v>94423.187659</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>643.672084</v>
+        <v>643.672253</v>
       </c>
       <c r="F135" t="n">
-        <v>6976.112379</v>
+        <v>6976.117282</v>
       </c>
       <c r="G135" t="n">
-        <v>15325.894509</v>
+        <v>15325.91836</v>
       </c>
       <c r="H135" t="n">
-        <v>27544.125379</v>
+        <v>27544.23401</v>
       </c>
       <c r="I135" t="n">
-        <v>43556.962565</v>
+        <v>43557.631252</v>
       </c>
       <c r="J135" t="n">
         <v>15447.021344</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>107.281569</v>
+        <v>107.279278</v>
       </c>
       <c r="F136" t="n">
-        <v>857.8282819999999</v>
+        <v>857.783782</v>
       </c>
       <c r="G136" t="n">
-        <v>1342.696946</v>
+        <v>1342.572291</v>
       </c>
       <c r="H136" t="n">
-        <v>1816.4734</v>
+        <v>1816.152724</v>
       </c>
       <c r="I136" t="n">
-        <v>2341.802044</v>
+        <v>2340.564786</v>
       </c>
       <c r="J136" t="n">
         <v>71131.34619</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1795.130101</v>
+        <v>1795.130431</v>
       </c>
       <c r="F137" t="n">
-        <v>15719.670434</v>
+        <v>15719.677819</v>
       </c>
       <c r="G137" t="n">
-        <v>26631.246624</v>
+        <v>26631.276304</v>
       </c>
       <c r="H137" t="n">
-        <v>38641.159963</v>
+        <v>38641.279326</v>
       </c>
       <c r="I137" t="n">
-        <v>52345.453374</v>
+        <v>52346.117568</v>
       </c>
       <c r="J137" t="n">
         <v>24335.488576</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>14.304272</v>
+        <v>14.303916</v>
       </c>
       <c r="F138" t="n">
-        <v>121.772964</v>
+        <v>121.764256</v>
       </c>
       <c r="G138" t="n">
-        <v>207.958478</v>
+        <v>207.926153</v>
       </c>
       <c r="H138" t="n">
-        <v>301.554333</v>
+        <v>301.449039</v>
       </c>
       <c r="I138" t="n">
-        <v>398.265579</v>
+        <v>397.809415</v>
       </c>
       <c r="J138" t="n">
         <v>23819.717465</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6.2e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F139" t="n">
-        <v>0.001686</v>
+        <v>0.000332</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00775</v>
+        <v>0.001526</v>
       </c>
       <c r="H139" t="n">
-        <v>0.033025</v>
+        <v>0.006502</v>
       </c>
       <c r="I139" t="n">
-        <v>0.187587</v>
+        <v>0.036932</v>
       </c>
       <c r="J139" t="n">
         <v>9649.365415</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>164.498141</v>
+        <v>164.49484</v>
       </c>
       <c r="F140" t="n">
-        <v>1350.187435</v>
+        <v>1350.119743</v>
       </c>
       <c r="G140" t="n">
-        <v>2343.175078</v>
+        <v>2342.931762</v>
       </c>
       <c r="H140" t="n">
-        <v>3661.381543</v>
+        <v>3660.490326</v>
       </c>
       <c r="I140" t="n">
-        <v>5426.173502</v>
+        <v>5421.330657</v>
       </c>
       <c r="J140" t="n">
         <v>331266.39921</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1476.86982</v>
+        <v>1476.870223</v>
       </c>
       <c r="F141" t="n">
-        <v>13632.976851</v>
+        <v>13632.987197</v>
       </c>
       <c r="G141" t="n">
-        <v>25978.736926</v>
+        <v>25978.782846</v>
       </c>
       <c r="H141" t="n">
-        <v>42484.634377</v>
+        <v>42484.830871</v>
       </c>
       <c r="I141" t="n">
-        <v>63152.490796</v>
+        <v>63153.64275</v>
       </c>
       <c r="J141" t="n">
         <v>8813.396999000001</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>414.81091</v>
+        <v>414.81101</v>
       </c>
       <c r="F142" t="n">
-        <v>6049.174725</v>
+        <v>6049.177713</v>
       </c>
       <c r="G142" t="n">
-        <v>18600.78578</v>
+        <v>18600.79018</v>
       </c>
       <c r="H142" t="n">
-        <v>42531.97454</v>
+        <v>42531.887733</v>
       </c>
       <c r="I142" t="n">
-        <v>77419.768754</v>
+        <v>77418.604145</v>
       </c>
       <c r="J142" t="n">
         <v>219080.571468</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102.771864</v>
+        <v>102.718653</v>
       </c>
       <c r="F146" t="n">
-        <v>108.09301</v>
+        <v>107.952951</v>
       </c>
       <c r="G146" t="n">
-        <v>110.6679</v>
+        <v>110.382921</v>
       </c>
       <c r="H146" t="n">
-        <v>124.515484</v>
+        <v>123.882218</v>
       </c>
       <c r="I146" t="n">
-        <v>156.257688</v>
+        <v>154.365067</v>
       </c>
       <c r="J146" t="n">
         <v>4242.608522</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1759.407723</v>
+        <v>1759.312146</v>
       </c>
       <c r="F147" t="n">
-        <v>2129.7483</v>
+        <v>2129.451796</v>
       </c>
       <c r="G147" t="n">
-        <v>2441.52075</v>
+        <v>2440.830464</v>
       </c>
       <c r="H147" t="n">
-        <v>2855.262825</v>
+        <v>2853.637116</v>
       </c>
       <c r="I147" t="n">
-        <v>3451.466035</v>
+        <v>3446.567172</v>
       </c>
       <c r="J147" t="n">
         <v>14410.774636</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>273606.454213</v>
+        <v>273606.603002</v>
       </c>
       <c r="F148" t="n">
-        <v>341978.43084</v>
+        <v>341978.867404</v>
       </c>
       <c r="G148" t="n">
-        <v>416170.96462</v>
+        <v>416171.939885</v>
       </c>
       <c r="H148" t="n">
-        <v>511709.449661</v>
+        <v>511711.708636</v>
       </c>
       <c r="I148" t="n">
-        <v>633168.596247</v>
+        <v>633175.38773</v>
       </c>
       <c r="J148" t="n">
         <v>744536.090712</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9149.977821</v>
+        <v>9149.308067</v>
       </c>
       <c r="F149" t="n">
-        <v>11089.343429</v>
+        <v>11087.328983</v>
       </c>
       <c r="G149" t="n">
-        <v>14639.936258</v>
+        <v>14634.603146</v>
       </c>
       <c r="H149" t="n">
-        <v>18969.483184</v>
+        <v>18955.548639</v>
       </c>
       <c r="I149" t="n">
-        <v>24263.360592</v>
+        <v>24218.833209</v>
       </c>
       <c r="J149" t="n">
         <v>101288.458121</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>111887.169492</v>
+        <v>111885.553883</v>
       </c>
       <c r="F150" t="n">
-        <v>133781.229676</v>
+        <v>133776.540572</v>
       </c>
       <c r="G150" t="n">
-        <v>172531.848123</v>
+        <v>172519.40315</v>
       </c>
       <c r="H150" t="n">
-        <v>209943.242763</v>
+        <v>209911.016916</v>
       </c>
       <c r="I150" t="n">
-        <v>247434.919759</v>
+        <v>247333.862776</v>
       </c>
       <c r="J150" t="n">
         <v>441337.826511</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>46425.106073</v>
+        <v>46424.242571</v>
       </c>
       <c r="F151" t="n">
-        <v>57756.818314</v>
+        <v>57754.188894</v>
       </c>
       <c r="G151" t="n">
-        <v>77635.363216</v>
+        <v>77628.125174</v>
       </c>
       <c r="H151" t="n">
-        <v>98206.586858</v>
+        <v>98187.35093099999</v>
       </c>
       <c r="I151" t="n">
-        <v>117852.541864</v>
+        <v>117792.072073</v>
       </c>
       <c r="J151" t="n">
         <v>228613.561535</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>86806.733517</v>
+        <v>86803.406036</v>
       </c>
       <c r="F152" t="n">
-        <v>113185.282237</v>
+        <v>113174.498396</v>
       </c>
       <c r="G152" t="n">
-        <v>149475.67789</v>
+        <v>149446.868296</v>
       </c>
       <c r="H152" t="n">
-        <v>181137.820281</v>
+        <v>181066.502704</v>
       </c>
       <c r="I152" t="n">
-        <v>207718.343952</v>
+        <v>207510.811457</v>
       </c>
       <c r="J152" t="n">
         <v>528397.514506</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>189655.101893</v>
+        <v>189661.121743</v>
       </c>
       <c r="F153" t="n">
-        <v>230927.13949</v>
+        <v>230945.742279</v>
       </c>
       <c r="G153" t="n">
-        <v>314089.737625</v>
+        <v>314139.730519</v>
       </c>
       <c r="H153" t="n">
-        <v>415717.188366</v>
+        <v>415845.480785</v>
       </c>
       <c r="I153" t="n">
-        <v>529846.37151</v>
+        <v>530239.006147</v>
       </c>
       <c r="J153" t="n">
         <v>67068.843513</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>43520.471205</v>
+        <v>43520.9277</v>
       </c>
       <c r="F154" t="n">
-        <v>55754.021254</v>
+        <v>55755.535277</v>
       </c>
       <c r="G154" t="n">
-        <v>73595.219767</v>
+        <v>73599.05259399999</v>
       </c>
       <c r="H154" t="n">
-        <v>89341.153628</v>
+        <v>89349.575105</v>
       </c>
       <c r="I154" t="n">
-        <v>101562.494402</v>
+        <v>101583.446418</v>
       </c>
       <c r="J154" t="n">
         <v>86297.91889299999</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>50430.99965</v>
+        <v>50431.000639</v>
       </c>
       <c r="F155" t="n">
-        <v>95164.079277</v>
+        <v>95164.083317</v>
       </c>
       <c r="G155" t="n">
-        <v>199483.959872</v>
+        <v>199483.973071</v>
       </c>
       <c r="H155" t="n">
-        <v>324029.846917</v>
+        <v>324029.876698</v>
       </c>
       <c r="I155" t="n">
-        <v>445215.856364</v>
+        <v>445215.909946</v>
       </c>
       <c r="J155" t="n">
-        <v>579213.059429</v>
+        <v>579213.148238</v>
       </c>
       <c r="K155" t="n">
-        <v>724086.962298</v>
+        <v>724087.10176</v>
       </c>
       <c r="L155" t="n">
-        <v>863165.317775</v>
+        <v>863165.52498</v>
       </c>
       <c r="M155" t="n">
-        <v>995223.172227</v>
+        <v>995223.468566</v>
       </c>
       <c r="N155" t="n">
-        <v>1131435.743228</v>
+        <v>1131436.159212</v>
       </c>
       <c r="O155" t="n">
-        <v>1282978.501967</v>
+        <v>1282979.082153</v>
       </c>
       <c r="P155" t="n">
-        <v>1443088.341593</v>
+        <v>1443089.143014</v>
       </c>
       <c r="Q155" t="n">
-        <v>1600419.193281</v>
+        <v>1600420.288423</v>
       </c>
       <c r="R155" t="n">
-        <v>1759546.806541</v>
+        <v>1759548.305556</v>
       </c>
       <c r="S155" t="n">
-        <v>1918608.531315</v>
+        <v>1918610.598681</v>
       </c>
       <c r="T155" t="n">
-        <v>2076494.070499</v>
+        <v>2076496.967428</v>
       </c>
       <c r="U155" t="n">
-        <v>2232886.799399</v>
+        <v>2232890.971933</v>
       </c>
       <c r="V155" t="n">
-        <v>2382070.067376</v>
+        <v>2382076.336012</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3637.839114</v>
+        <v>3637.838424</v>
       </c>
       <c r="F156" t="n">
-        <v>6400.766175</v>
+        <v>6400.763236</v>
       </c>
       <c r="G156" t="n">
-        <v>12323.917158</v>
+        <v>12323.907379</v>
       </c>
       <c r="H156" t="n">
-        <v>18090.425552</v>
+        <v>18090.403726</v>
       </c>
       <c r="I156" t="n">
-        <v>22386.874408</v>
+        <v>22386.835737</v>
       </c>
       <c r="J156" t="n">
-        <v>26219.52259</v>
+        <v>26219.459156</v>
       </c>
       <c r="K156" t="n">
-        <v>29413.613243</v>
+        <v>29413.515169</v>
       </c>
       <c r="L156" t="n">
-        <v>31413.384822</v>
+        <v>31413.242078</v>
       </c>
       <c r="M156" t="n">
-        <v>32503.074714</v>
+        <v>32502.874897</v>
       </c>
       <c r="N156" t="n">
-        <v>33205.526727</v>
+        <v>33205.251623</v>
       </c>
       <c r="O156" t="n">
-        <v>33835.377265</v>
+        <v>33835.000698</v>
       </c>
       <c r="P156" t="n">
-        <v>34178.142762</v>
+        <v>34177.631607</v>
       </c>
       <c r="Q156" t="n">
-        <v>34020.741289</v>
+        <v>34020.05324</v>
       </c>
       <c r="R156" t="n">
-        <v>33582.572036</v>
+        <v>33581.644979</v>
       </c>
       <c r="S156" t="n">
-        <v>32892.437859</v>
+        <v>32891.183078</v>
       </c>
       <c r="T156" t="n">
-        <v>32030.292844</v>
+        <v>32028.573487</v>
       </c>
       <c r="U156" t="n">
-        <v>31078.636335</v>
+        <v>31076.219831</v>
       </c>
       <c r="V156" t="n">
-        <v>30036.64564</v>
+        <v>30033.108863</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1108.627953</v>
+        <v>1108.627898</v>
       </c>
       <c r="F157" t="n">
-        <v>2459.818609</v>
+        <v>2459.81819</v>
       </c>
       <c r="G157" t="n">
-        <v>5773.808744</v>
+        <v>5773.80654</v>
       </c>
       <c r="H157" t="n">
-        <v>9500.41662</v>
+        <v>9500.410373000001</v>
       </c>
       <c r="I157" t="n">
-        <v>12307.691922</v>
+        <v>12307.680047</v>
       </c>
       <c r="J157" t="n">
-        <v>14445.005265</v>
+        <v>14444.986483</v>
       </c>
       <c r="K157" t="n">
-        <v>16147.000811</v>
+        <v>16146.973242</v>
       </c>
       <c r="L157" t="n">
-        <v>17339.580942</v>
+        <v>17339.542045</v>
       </c>
       <c r="M157" t="n">
-        <v>18223.458484</v>
+        <v>18223.404429</v>
       </c>
       <c r="N157" t="n">
-        <v>18938.953813</v>
+        <v>18938.879622</v>
       </c>
       <c r="O157" t="n">
-        <v>19563.323192</v>
+        <v>19563.222298</v>
       </c>
       <c r="P157" t="n">
-        <v>19920.13538</v>
+        <v>19920.000462</v>
       </c>
       <c r="Q157" t="n">
-        <v>19828.393306</v>
+        <v>19828.216891</v>
       </c>
       <c r="R157" t="n">
-        <v>19437.776794</v>
+        <v>19437.548644</v>
       </c>
       <c r="S157" t="n">
-        <v>18818.954519</v>
+        <v>18818.660345</v>
       </c>
       <c r="T157" t="n">
-        <v>18062.927625</v>
+        <v>18062.545133</v>
       </c>
       <c r="U157" t="n">
-        <v>17216.61</v>
+        <v>17216.10238</v>
       </c>
       <c r="V157" t="n">
-        <v>16292.430092</v>
+        <v>16291.730988</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>26719.26607</v>
+        <v>26719.265641</v>
       </c>
       <c r="F158" t="n">
-        <v>41640.743226</v>
+        <v>41640.741839</v>
       </c>
       <c r="G158" t="n">
-        <v>70485.382539</v>
+        <v>70485.379187</v>
       </c>
       <c r="H158" t="n">
-        <v>94275.78</v>
+        <v>94275.77389900001</v>
       </c>
       <c r="I158" t="n">
-        <v>110188.392508</v>
+        <v>110188.382465</v>
       </c>
       <c r="J158" t="n">
-        <v>124784.756819</v>
+        <v>124784.740164</v>
       </c>
       <c r="K158" t="n">
-        <v>137692.080135</v>
+        <v>137692.05289</v>
       </c>
       <c r="L158" t="n">
-        <v>145830.078361</v>
+        <v>145830.036017</v>
       </c>
       <c r="M158" t="n">
-        <v>149671.283853</v>
+        <v>149671.221642</v>
       </c>
       <c r="N158" t="n">
-        <v>151404.470127</v>
+        <v>151404.381967</v>
       </c>
       <c r="O158" t="n">
-        <v>152811.555177</v>
+        <v>152811.432369</v>
       </c>
       <c r="P158" t="n">
-        <v>152718.909999</v>
+        <v>152718.742565</v>
       </c>
       <c r="Q158" t="n">
-        <v>149887.88609</v>
+        <v>149887.66345</v>
       </c>
       <c r="R158" t="n">
-        <v>146322.23145</v>
+        <v>146321.934713</v>
       </c>
       <c r="S158" t="n">
-        <v>142683.462262</v>
+        <v>142683.060477</v>
       </c>
       <c r="T158" t="n">
-        <v>139208.017013</v>
+        <v>139207.460318</v>
       </c>
       <c r="U158" t="n">
-        <v>135562.763979</v>
+        <v>135561.972302</v>
       </c>
       <c r="V158" t="n">
-        <v>131206.801845</v>
+        <v>131205.638156</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>472.486373</v>
+        <v>472.486361</v>
       </c>
       <c r="F159" t="n">
-        <v>799.693425</v>
+        <v>799.6933759999999</v>
       </c>
       <c r="G159" t="n">
-        <v>1507.511194</v>
+        <v>1507.511036</v>
       </c>
       <c r="H159" t="n">
-        <v>2177.505368</v>
+        <v>2177.505024</v>
       </c>
       <c r="I159" t="n">
-        <v>2678.652808</v>
+        <v>2678.652199</v>
       </c>
       <c r="J159" t="n">
-        <v>3126.897577</v>
+        <v>3126.896578</v>
       </c>
       <c r="K159" t="n">
-        <v>3557.151874</v>
+        <v>3557.150265</v>
       </c>
       <c r="L159" t="n">
-        <v>3873.946256</v>
+        <v>3873.9438</v>
       </c>
       <c r="M159" t="n">
-        <v>4059.703561</v>
+        <v>4059.700037</v>
       </c>
       <c r="N159" t="n">
-        <v>4160.405379</v>
+        <v>4160.400538</v>
       </c>
       <c r="O159" t="n">
-        <v>4246.235891</v>
+        <v>4246.229297</v>
       </c>
       <c r="P159" t="n">
-        <v>4297.94895</v>
+        <v>4297.940017</v>
       </c>
       <c r="Q159" t="n">
-        <v>4262.184298</v>
+        <v>4262.172432</v>
       </c>
       <c r="R159" t="n">
-        <v>4142.77698</v>
+        <v>4142.761584</v>
       </c>
       <c r="S159" t="n">
-        <v>3946.85157</v>
+        <v>3946.832004</v>
       </c>
       <c r="T159" t="n">
-        <v>3702.249262</v>
+        <v>3702.224508</v>
       </c>
       <c r="U159" t="n">
-        <v>3443.379958</v>
+        <v>3443.348079</v>
       </c>
       <c r="V159" t="n">
-        <v>3191.363264</v>
+        <v>3191.320437</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14438.43584</v>
+        <v>14438.436037</v>
       </c>
       <c r="F160" t="n">
-        <v>26412.708508</v>
+        <v>26412.709262</v>
       </c>
       <c r="G160" t="n">
-        <v>55060.375352</v>
+        <v>55060.377647</v>
       </c>
       <c r="H160" t="n">
-        <v>88992.009504</v>
+        <v>88992.01424</v>
       </c>
       <c r="I160" t="n">
-        <v>121184.127951</v>
+        <v>121184.135566</v>
       </c>
       <c r="J160" t="n">
-        <v>153900.90028</v>
+        <v>153900.911341</v>
       </c>
       <c r="K160" t="n">
-        <v>186084.391598</v>
+        <v>186084.406635</v>
       </c>
       <c r="L160" t="n">
-        <v>212721.879644</v>
+        <v>212721.89888</v>
       </c>
       <c r="M160" t="n">
-        <v>236000.212161</v>
+        <v>236000.235429</v>
       </c>
       <c r="N160" t="n">
-        <v>260341.517726</v>
+        <v>260341.544038</v>
       </c>
       <c r="O160" t="n">
-        <v>289135.244508</v>
+        <v>289135.271186</v>
       </c>
       <c r="P160" t="n">
-        <v>320734.401317</v>
+        <v>320734.422334</v>
       </c>
       <c r="Q160" t="n">
-        <v>352408.271736</v>
+        <v>352408.275564</v>
       </c>
       <c r="R160" t="n">
-        <v>384608.516199</v>
+        <v>384608.484524</v>
       </c>
       <c r="S160" t="n">
-        <v>416641.362475</v>
+        <v>416641.265415</v>
       </c>
       <c r="T160" t="n">
-        <v>449123.352758</v>
+        <v>449123.139125</v>
       </c>
       <c r="U160" t="n">
-        <v>482738.160329</v>
+        <v>482737.735474</v>
       </c>
       <c r="V160" t="n">
-        <v>517341.211784</v>
+        <v>517340.385544</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6.909482</v>
+        <v>6.895356</v>
       </c>
       <c r="F162" t="n">
-        <v>5.612892</v>
+        <v>5.589797</v>
       </c>
       <c r="G162" t="n">
-        <v>6.209558</v>
+        <v>6.167957</v>
       </c>
       <c r="H162" t="n">
-        <v>7.113354</v>
+        <v>7.03186</v>
       </c>
       <c r="I162" t="n">
-        <v>8.991057</v>
+        <v>8.770769</v>
       </c>
       <c r="J162" t="n">
         <v>5899.620992</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1008.970828</v>
+        <v>1008.971659</v>
       </c>
       <c r="F163" t="n">
-        <v>1316.681349</v>
+        <v>1316.683263</v>
       </c>
       <c r="G163" t="n">
-        <v>2299.450427</v>
+        <v>2299.454146</v>
       </c>
       <c r="H163" t="n">
-        <v>3460.501834</v>
+        <v>3460.50717</v>
       </c>
       <c r="I163" t="n">
-        <v>4655.729717</v>
+        <v>4655.73799</v>
       </c>
       <c r="J163" t="n">
         <v>5644.970866</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>7129.934628</v>
+        <v>7129.942354</v>
       </c>
       <c r="F164" t="n">
-        <v>10166.38621</v>
+        <v>10166.407878</v>
       </c>
       <c r="G164" t="n">
-        <v>18877.19605</v>
+        <v>18877.254474</v>
       </c>
       <c r="H164" t="n">
-        <v>30438.330199</v>
+        <v>30438.466253</v>
       </c>
       <c r="I164" t="n">
-        <v>44031.012723</v>
+        <v>44031.383861</v>
       </c>
       <c r="J164" t="n">
         <v>49538.285104</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>47892.630455</v>
+        <v>47892.710277</v>
       </c>
       <c r="F165" t="n">
-        <v>60786.256326</v>
+        <v>60786.498123</v>
       </c>
       <c r="G165" t="n">
-        <v>90895.54485200001</v>
+        <v>90896.248376</v>
       </c>
       <c r="H165" t="n">
-        <v>124319.516673</v>
+        <v>124321.44514</v>
       </c>
       <c r="I165" t="n">
-        <v>162234.262509</v>
+        <v>162240.714337</v>
       </c>
       <c r="J165" t="n">
         <v>11646.998714</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>32776.042208</v>
+        <v>32776.092348</v>
       </c>
       <c r="F166" t="n">
-        <v>38775.822909</v>
+        <v>38775.962481</v>
       </c>
       <c r="G166" t="n">
-        <v>59498.440748</v>
+        <v>59498.850266</v>
       </c>
       <c r="H166" t="n">
-        <v>82705.82122300001</v>
+        <v>82706.948093</v>
       </c>
       <c r="I166" t="n">
-        <v>106761.651306</v>
+        <v>106765.35703</v>
       </c>
       <c r="J166" t="n">
         <v>23534.141692</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>50982.603541</v>
+        <v>50982.545766</v>
       </c>
       <c r="F167" t="n">
-        <v>57798.006373</v>
+        <v>57797.816261</v>
       </c>
       <c r="G167" t="n">
-        <v>87019.13286</v>
+        <v>87018.491503</v>
       </c>
       <c r="H167" t="n">
-        <v>123093.239316</v>
+        <v>123091.259149</v>
       </c>
       <c r="I167" t="n">
-        <v>166473.872792</v>
+        <v>166466.685606</v>
       </c>
       <c r="J167" t="n">
         <v>444185.10765</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>307.819433</v>
+        <v>307.819538</v>
       </c>
       <c r="F168" t="n">
-        <v>382.176161</v>
+        <v>382.176276</v>
       </c>
       <c r="G168" t="n">
-        <v>615.82381</v>
+        <v>615.823617</v>
       </c>
       <c r="H168" t="n">
-        <v>898.429042</v>
+        <v>898.427471</v>
       </c>
       <c r="I168" t="n">
-        <v>1221.774687</v>
+        <v>1221.767668</v>
       </c>
       <c r="J168" t="n">
         <v>1819.298092</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>71424.167881</v>
+        <v>71424.24234500001</v>
       </c>
       <c r="F169" t="n">
-        <v>86863.043062</v>
+        <v>86863.24418199999</v>
       </c>
       <c r="G169" t="n">
-        <v>137553.870433</v>
+        <v>137554.452403</v>
       </c>
       <c r="H169" t="n">
-        <v>205019.036408</v>
+        <v>205020.688522</v>
       </c>
       <c r="I169" t="n">
-        <v>293652.548656</v>
+        <v>293658.358696</v>
       </c>
       <c r="J169" t="n">
         <v>223576.58232</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>8663.424818</v>
+        <v>8663.435153</v>
       </c>
       <c r="F170" t="n">
-        <v>13239.143716</v>
+        <v>13239.176325</v>
       </c>
       <c r="G170" t="n">
-        <v>24971.194852</v>
+        <v>24971.296507</v>
       </c>
       <c r="H170" t="n">
-        <v>40160.69103</v>
+        <v>40160.982971</v>
       </c>
       <c r="I170" t="n">
-        <v>57869.517297</v>
+        <v>57870.538186</v>
       </c>
       <c r="J170" t="n">
         <v>45628.987878</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>34198.179027</v>
+        <v>34198.199038</v>
       </c>
       <c r="F171" t="n">
-        <v>40357.585924</v>
+        <v>40357.625331</v>
       </c>
       <c r="G171" t="n">
-        <v>61965.362304</v>
+        <v>61965.434059</v>
       </c>
       <c r="H171" t="n">
-        <v>86149.644717</v>
+        <v>86149.764865</v>
       </c>
       <c r="I171" t="n">
-        <v>111495.022265</v>
+        <v>111495.303668</v>
       </c>
       <c r="J171" t="n">
         <v>130590.743785</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3149.394594</v>
+        <v>3149.076381</v>
       </c>
       <c r="F172" t="n">
-        <v>3575.504756</v>
+        <v>3574.542586</v>
       </c>
       <c r="G172" t="n">
-        <v>5147.621935</v>
+        <v>5144.784613</v>
       </c>
       <c r="H172" t="n">
-        <v>6821.470756</v>
+        <v>6813.89702</v>
       </c>
       <c r="I172" t="n">
-        <v>8744.448316</v>
+        <v>8720.0591</v>
       </c>
       <c r="J172" t="n">
         <v>713417.934604</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>692.622247</v>
+        <v>692.623252</v>
       </c>
       <c r="F173" t="n">
-        <v>1006.183199</v>
+        <v>1006.186536</v>
       </c>
       <c r="G173" t="n">
-        <v>1834.871788</v>
+        <v>1834.883092</v>
       </c>
       <c r="H173" t="n">
-        <v>2897.580437</v>
+        <v>2897.615205</v>
       </c>
       <c r="I173" t="n">
-        <v>4185.056059</v>
+        <v>4185.183021</v>
       </c>
       <c r="J173" t="n">
         <v>1616.56529</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>47821.761624</v>
+        <v>47821.645219</v>
       </c>
       <c r="F174" t="n">
-        <v>53876.736483</v>
+        <v>53876.360433</v>
       </c>
       <c r="G174" t="n">
-        <v>79564.14849000001</v>
+        <v>79562.919754</v>
       </c>
       <c r="H174" t="n">
-        <v>109289.516899</v>
+        <v>109285.867656</v>
       </c>
       <c r="I174" t="n">
-        <v>143058.139719</v>
+        <v>143045.357882</v>
       </c>
       <c r="J174" t="n">
         <v>588807.262965</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1436.998215</v>
+        <v>1437.000531</v>
       </c>
       <c r="F175" t="n">
-        <v>2458.920775</v>
+        <v>2458.929987</v>
       </c>
       <c r="G175" t="n">
-        <v>5271.779266</v>
+        <v>5271.816334</v>
       </c>
       <c r="H175" t="n">
-        <v>9599.521814</v>
+        <v>9599.652844</v>
       </c>
       <c r="I175" t="n">
-        <v>15682.695228</v>
+        <v>15683.230008</v>
       </c>
       <c r="J175" t="n">
         <v>4879.533141</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>121.895378</v>
+        <v>121.895319</v>
       </c>
       <c r="F176" t="n">
-        <v>129.715778</v>
+        <v>129.715585</v>
       </c>
       <c r="G176" t="n">
-        <v>189.694535</v>
+        <v>189.693848</v>
       </c>
       <c r="H176" t="n">
-        <v>264.807073</v>
+        <v>264.804856</v>
       </c>
       <c r="I176" t="n">
-        <v>357.069178</v>
+        <v>357.060718</v>
       </c>
       <c r="J176" t="n">
         <v>740.6680270000001</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>191988.302794</v>
+        <v>191988.562672</v>
       </c>
       <c r="F177" t="n">
-        <v>297061.49406</v>
+        <v>297062.355554</v>
       </c>
       <c r="G177" t="n">
-        <v>560215.5758850001</v>
+        <v>560218.35015</v>
       </c>
       <c r="H177" t="n">
-        <v>876220.758698</v>
+        <v>876228.63272</v>
       </c>
       <c r="I177" t="n">
-        <v>1198560.85426</v>
+        <v>1198587.185657</v>
       </c>
       <c r="J177" t="n">
         <v>730665.075659</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>306.594167</v>
+        <v>306.594127</v>
       </c>
       <c r="F178" t="n">
-        <v>406.319995</v>
+        <v>406.319557</v>
       </c>
       <c r="G178" t="n">
-        <v>685.699739</v>
+        <v>685.697478</v>
       </c>
       <c r="H178" t="n">
-        <v>1045.938263</v>
+        <v>1045.9299</v>
       </c>
       <c r="I178" t="n">
-        <v>1483.722442</v>
+        <v>1483.689928</v>
       </c>
       <c r="J178" t="n">
         <v>3066.320439</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>211.848681</v>
+        <v>211.848667</v>
       </c>
       <c r="F179" t="n">
-        <v>246.987232</v>
+        <v>246.987046</v>
       </c>
       <c r="G179" t="n">
-        <v>388.238067</v>
+        <v>388.237024</v>
       </c>
       <c r="H179" t="n">
-        <v>559.263864</v>
+        <v>559.259905</v>
       </c>
       <c r="I179" t="n">
-        <v>758.236388</v>
+        <v>758.220475</v>
       </c>
       <c r="J179" t="n">
         <v>1529.267382</v>
@@ -14130,25 +14130,25 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-4e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>-3e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="G181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="H181" t="n">
         <v>6e-06</v>
       </c>
-      <c r="H181" t="n">
-        <v>-3e-06</v>
-      </c>
       <c r="I181" t="n">
-        <v>4e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="J181" t="n">
         <v>4e-06</v>
       </c>
       <c r="K181" t="n">
-        <v>-5e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="L181" t="n">
         <v>-1e-06</v>
@@ -14160,10 +14160,10 @@
         <v>-5e-06</v>
       </c>
       <c r="O181" t="n">
-        <v>-0</v>
+        <v>-1e-06</v>
       </c>
       <c r="P181" t="n">
-        <v>1e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="Q181" t="n">
         <v>-4e-06</v>
@@ -14175,13 +14175,13 @@
         <v>-2e-06</v>
       </c>
       <c r="T181" t="n">
-        <v>1e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>8e-06</v>
+        <v>9e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-1e-06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
